--- a/database/event/8043/event_8043_evp_summary.xlsx
+++ b/database/event/8043/event_8043_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>10.8458</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3.7783</v>
       </c>
       <c r="D2" t="n">
         <v>3.9601</v>
@@ -545,7 +545,7 @@
         <v>7.2947</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2.5412</v>
       </c>
       <c r="D3" t="n">
         <v>2.5255</v>
@@ -591,7 +591,7 @@
         <v>6.8841</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2.3982</v>
       </c>
       <c r="D4" t="n">
         <v>2.3597</v>
@@ -637,7 +637,7 @@
         <v>6.6536</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2.3179</v>
       </c>
       <c r="D5" t="n">
         <v>2.2665</v>
@@ -683,7 +683,7 @@
         <v>6.6476</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.3158</v>
       </c>
       <c r="D6" t="n">
         <v>2.2641</v>
@@ -729,7 +729,7 @@
         <v>6.4836</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.2587</v>
       </c>
       <c r="D7" t="n">
         <v>2.1979</v>
@@ -775,7 +775,7 @@
         <v>6.4821</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.2582</v>
       </c>
       <c r="D8" t="n">
         <v>2.1973</v>
@@ -821,7 +821,7 @@
         <v>6.4691</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.2536</v>
       </c>
       <c r="D9" t="n">
         <v>2.192</v>
@@ -867,7 +867,7 @@
         <v>6.0614</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.1116</v>
       </c>
       <c r="D10" t="n">
         <v>2.0273</v>
@@ -913,7 +913,7 @@
         <v>4.4426</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.5477</v>
       </c>
       <c r="D11" t="n">
         <v>1.3733</v>
@@ -959,7 +959,7 @@
         <v>4.2906</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.4947</v>
       </c>
       <c r="D12" t="n">
         <v>1.3119</v>
@@ -1005,7 +1005,7 @@
         <v>4.0583</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.4138</v>
       </c>
       <c r="D13" t="n">
         <v>1.2181</v>
@@ -1051,7 +1051,7 @@
         <v>4.0565</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.4132</v>
       </c>
       <c r="D14" t="n">
         <v>1.2174</v>
@@ -1097,7 +1097,7 @@
         <v>4.0078</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.3962</v>
       </c>
       <c r="D15" t="n">
         <v>1.1977</v>
@@ -1143,7 +1143,7 @@
         <v>3.9066</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.3609</v>
       </c>
       <c r="D16" t="n">
         <v>1.1568</v>
@@ -1189,7 +1189,7 @@
         <v>3.6576</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.2742</v>
       </c>
       <c r="D17" t="n">
         <v>1.0562</v>
@@ -1235,7 +1235,7 @@
         <v>3.5857</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.2491</v>
       </c>
       <c r="D18" t="n">
         <v>1.0272</v>
@@ -1281,7 +1281,7 @@
         <v>3.5633</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.2413</v>
       </c>
       <c r="D19" t="n">
         <v>1.0181</v>
@@ -1327,7 +1327,7 @@
         <v>3.2785</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.1421</v>
       </c>
       <c r="D20" t="n">
         <v>0.9031</v>
@@ -1373,7 +1373,7 @@
         <v>3.1908</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.1116</v>
       </c>
       <c r="D21" t="n">
         <v>0.8677</v>
@@ -1419,7 +1419,7 @@
         <v>3.1818</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.1084</v>
       </c>
       <c r="D22" t="n">
         <v>0.864</v>
@@ -1465,7 +1465,7 @@
         <v>3.1498</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.0973</v>
       </c>
       <c r="D23" t="n">
         <v>0.8511</v>
@@ -1511,7 +1511,7 @@
         <v>3.1269</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.0893</v>
       </c>
       <c r="D24" t="n">
         <v>0.8418</v>
@@ -1557,7 +1557,7 @@
         <v>2.9871</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.0406</v>
       </c>
       <c r="D25" t="n">
         <v>0.7854</v>
@@ -1603,7 +1603,7 @@
         <v>2.9842</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.0396</v>
       </c>
       <c r="D26" t="n">
         <v>0.7842</v>
@@ -1649,7 +1649,7 @@
         <v>2.875</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1.0016</v>
       </c>
       <c r="D27" t="n">
         <v>0.7401</v>
@@ -1695,7 +1695,7 @@
         <v>2.5482</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.8877</v>
       </c>
       <c r="D28" t="n">
         <v>0.6081</v>
@@ -1741,7 +1741,7 @@
         <v>2.5085</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.8739</v>
       </c>
       <c r="D29" t="n">
         <v>0.592</v>
@@ -1787,7 +1787,7 @@
         <v>2.1876</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.7621</v>
       </c>
       <c r="D30" t="n">
         <v>0.4624</v>
@@ -1833,7 +1833,7 @@
         <v>2.1785</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.7589</v>
       </c>
       <c r="D31" t="n">
         <v>0.4587</v>
@@ -1879,7 +1879,7 @@
         <v>2.0828</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.7256</v>
       </c>
       <c r="D32" t="n">
         <v>0.42</v>
@@ -1925,7 +1925,7 @@
         <v>1.9001</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.6619</v>
       </c>
       <c r="D33" t="n">
         <v>0.3462</v>
@@ -1971,7 +1971,7 @@
         <v>1.8489</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.6441</v>
       </c>
       <c r="D34" t="n">
         <v>0.3256</v>
@@ -2017,7 +2017,7 @@
         <v>1.6924</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.5896</v>
       </c>
       <c r="D35" t="n">
         <v>0.2623</v>
@@ -2063,7 +2063,7 @@
         <v>1.6672</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.5808</v>
       </c>
       <c r="D36" t="n">
         <v>0.2521</v>
@@ -2109,7 +2109,7 @@
         <v>1.6022</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.5582</v>
       </c>
       <c r="D37" t="n">
         <v>0.2259</v>
@@ -2155,7 +2155,7 @@
         <v>1.3393</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.4666</v>
       </c>
       <c r="D38" t="n">
         <v>0.1197</v>
@@ -2201,7 +2201,7 @@
         <v>1.2942</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.4509</v>
       </c>
       <c r="D39" t="n">
         <v>0.1015</v>
@@ -2247,7 +2247,7 @@
         <v>1.2757</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.4444</v>
       </c>
       <c r="D40" t="n">
         <v>0.094</v>
@@ -2293,7 +2293,7 @@
         <v>1.2196</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.4249</v>
       </c>
       <c r="D41" t="n">
         <v>0.0713</v>
@@ -2339,7 +2339,7 @@
         <v>1.166</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.4062</v>
       </c>
       <c r="D42" t="n">
         <v>0.0497</v>
@@ -2385,7 +2385,7 @@
         <v>1.1172</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.3892</v>
       </c>
       <c r="D43" t="n">
         <v>0.03</v>
@@ -2431,7 +2431,7 @@
         <v>1.0531</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.3669</v>
       </c>
       <c r="D44" t="n">
         <v>0.0041</v>
@@ -2477,7 +2477,7 @@
         <v>1.0215</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.3559</v>
       </c>
       <c r="D45" t="n">
         <v>-0.008699999999999999</v>
@@ -2523,7 +2523,7 @@
         <v>0.9727</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.3389</v>
       </c>
       <c r="D46" t="n">
         <v>-0.0284</v>
@@ -2569,7 +2569,7 @@
         <v>0.8849</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.3083</v>
       </c>
       <c r="D47" t="n">
         <v>-0.0639</v>
@@ -2615,7 +2615,7 @@
         <v>0.6338</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.2208</v>
       </c>
       <c r="D48" t="n">
         <v>-0.1653</v>
@@ -2661,7 +2661,7 @@
         <v>0.4283</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.1492</v>
       </c>
       <c r="D49" t="n">
         <v>-0.2483</v>
@@ -2707,7 +2707,7 @@
         <v>0.3691</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.1286</v>
       </c>
       <c r="D50" t="n">
         <v>-0.2723</v>
@@ -2753,7 +2753,7 @@
         <v>0.3611</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.1258</v>
       </c>
       <c r="D51" t="n">
         <v>-0.2755</v>
@@ -2799,7 +2799,7 @@
         <v>0.3119</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.1087</v>
       </c>
       <c r="D52" t="n">
         <v>-0.2954</v>
@@ -2845,7 +2845,7 @@
         <v>0.2924</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.1019</v>
       </c>
       <c r="D53" t="n">
         <v>-0.3032</v>
@@ -2891,7 +2891,7 @@
         <v>0.1478</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.0515</v>
       </c>
       <c r="D54" t="n">
         <v>-0.3617</v>
@@ -2937,7 +2937,7 @@
         <v>0.0587</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.0204</v>
       </c>
       <c r="D55" t="n">
         <v>-0.3976</v>
@@ -2983,7 +2983,7 @@
         <v>-0.09420000000000001</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.0328</v>
       </c>
       <c r="D56" t="n">
         <v>-0.4594</v>
@@ -3029,7 +3029,7 @@
         <v>-0.2376</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.0828</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5173</v>
@@ -3075,7 +3075,7 @@
         <v>-0.2635</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="D58" t="n">
         <v>-0.5278</v>
@@ -3121,7 +3121,7 @@
         <v>-0.5684</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.198</v>
       </c>
       <c r="D59" t="n">
         <v>-0.651</v>
@@ -3167,7 +3167,7 @@
         <v>-0.6225000000000001</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.2169</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6728</v>
@@ -3213,7 +3213,7 @@
         <v>-0.6278</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.2187</v>
       </c>
       <c r="D61" t="n">
         <v>-0.675</v>
@@ -3259,7 +3259,7 @@
         <v>-0.6414</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.2234</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6805</v>
@@ -3305,7 +3305,7 @@
         <v>-0.7356</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.2563</v>
       </c>
       <c r="D63" t="n">
         <v>-0.7185</v>
@@ -3351,7 +3351,7 @@
         <v>-0.7932</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.2763</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7418</v>
@@ -3397,7 +3397,7 @@
         <v>-0.9688</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.3375</v>
       </c>
       <c r="D65" t="n">
         <v>-0.8127</v>
@@ -3443,7 +3443,7 @@
         <v>-1.0988</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.3828</v>
       </c>
       <c r="D66" t="n">
         <v>-0.8653</v>
@@ -3489,7 +3489,7 @@
         <v>-1.1892</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.4143</v>
       </c>
       <c r="D67" t="n">
         <v>-0.9018</v>
@@ -3535,7 +3535,7 @@
         <v>-1.4517</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.5057</v>
       </c>
       <c r="D68" t="n">
         <v>-1.0078</v>
@@ -3581,7 +3581,7 @@
         <v>-1.716</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.5978</v>
       </c>
       <c r="D69" t="n">
         <v>-1.1146</v>
@@ -3627,7 +3627,7 @@
         <v>-1.723</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.6002</v>
       </c>
       <c r="D70" t="n">
         <v>-1.1174</v>
@@ -3673,7 +3673,7 @@
         <v>-2.1106</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.7353</v>
       </c>
       <c r="D71" t="n">
         <v>-1.274</v>
@@ -3719,7 +3719,7 @@
         <v>-2.172</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.7567</v>
       </c>
       <c r="D72" t="n">
         <v>-1.2988</v>
@@ -3765,7 +3765,7 @@
         <v>-2.2645</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.7889</v>
       </c>
       <c r="D73" t="n">
         <v>-1.3362</v>
@@ -3811,7 +3811,7 @@
         <v>-2.3971</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.8351</v>
       </c>
       <c r="D74" t="n">
         <v>-1.3897</v>
@@ -3857,7 +3857,7 @@
         <v>-2.6647</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.9283</v>
       </c>
       <c r="D75" t="n">
         <v>-1.4978</v>
@@ -3903,7 +3903,7 @@
         <v>-2.8258</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-0.9844000000000001</v>
       </c>
       <c r="D76" t="n">
         <v>-1.5629</v>
@@ -3949,7 +3949,7 @@
         <v>-2.879</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.003</v>
       </c>
       <c r="D77" t="n">
         <v>-1.5844</v>
@@ -3995,7 +3995,7 @@
         <v>-2.9711</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.035</v>
       </c>
       <c r="D78" t="n">
         <v>-1.6216</v>
@@ -4041,7 +4041,7 @@
         <v>-3.4695</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.2087</v>
       </c>
       <c r="D79" t="n">
         <v>-1.823</v>
@@ -4087,7 +4087,7 @@
         <v>-4.8902</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.7036</v>
       </c>
       <c r="D80" t="n">
         <v>-2.3969</v>
@@ -4133,7 +4133,7 @@
         <v>-6.3407</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.2089</v>
       </c>
       <c r="D81" t="n">
         <v>-2.9829</v>

--- a/database/event/8043/event_8043_evp_summary.xlsx
+++ b/database/event/8043/event_8043_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.8458</v>
+        <v>10.8327</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7783</v>
+        <v>3.7738</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9601</v>
+        <v>3.8718</v>
       </c>
       <c r="E2" t="n">
-        <v>10.8458</v>
+        <v>10.8327</v>
       </c>
       <c r="F2" t="n">
-        <v>4.9779</v>
+        <v>4.9648</v>
       </c>
       <c r="G2" t="n">
         <v>5.868</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5022</v>
+        <v>5.4817</v>
       </c>
       <c r="I2" t="n">
         <v>5.5278</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.2947</v>
+        <v>7.2825</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5412</v>
+        <v>2.537</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5255</v>
+        <v>2.4574</v>
       </c>
       <c r="E3" t="n">
-        <v>7.2947</v>
+        <v>7.2825</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2703</v>
+        <v>3.2581</v>
       </c>
       <c r="G3" t="n">
         <v>4.0244</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2703</v>
+        <v>3.2581</v>
       </c>
       <c r="I3" t="n">
         <v>3.2855</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.8841</v>
+        <v>6.862</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3982</v>
+        <v>2.3905</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3597</v>
+        <v>2.2899</v>
       </c>
       <c r="E4" t="n">
-        <v>6.8841</v>
+        <v>6.862</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4393</v>
+        <v>4.4171</v>
       </c>
       <c r="G4" t="n">
         <v>2.4448</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6577</v>
+        <v>4.623</v>
       </c>
       <c r="I4" t="n">
         <v>4.7012</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.6536</v>
+        <v>6.6476</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3179</v>
+        <v>2.3158</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2665</v>
+        <v>2.2045</v>
       </c>
       <c r="E5" t="n">
-        <v>6.6536</v>
+        <v>6.6476</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8007</v>
+        <v>5.0337</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8529</v>
+        <v>1.6139</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8007</v>
+        <v>5.5897</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8137</v>
+        <v>5.5897</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8529</v>
+        <v>1.6139</v>
       </c>
       <c r="K5" t="n">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="L5" t="n">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="M5" t="n">
-        <v>6.6666</v>
+        <v>7.2036</v>
       </c>
       <c r="N5" t="n">
-        <v>463</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.6476</v>
+        <v>6.6432</v>
       </c>
       <c r="C6" t="n">
-        <v>2.3158</v>
+        <v>2.3143</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2641</v>
+        <v>2.2027</v>
       </c>
       <c r="E6" t="n">
-        <v>6.6476</v>
+        <v>6.6432</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0337</v>
+        <v>2.7902</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6139</v>
+        <v>3.8529</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5897</v>
+        <v>2.7902</v>
       </c>
       <c r="I6" t="n">
-        <v>5.5897</v>
+        <v>2.8137</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6139</v>
+        <v>3.8529</v>
       </c>
       <c r="K6" t="n">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="L6" t="n">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="M6" t="n">
-        <v>7.2036</v>
+        <v>6.6666</v>
       </c>
       <c r="N6" t="n">
-        <v>323</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7">
@@ -732,7 +732,7 @@
         <v>2.2587</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1979</v>
+        <v>2.1392</v>
       </c>
       <c r="E7" t="n">
         <v>6.4836</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.4821</v>
+        <v>6.4592</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2582</v>
+        <v>2.2502</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1973</v>
+        <v>2.1294</v>
       </c>
       <c r="E8" t="n">
-        <v>6.4821</v>
+        <v>6.4592</v>
       </c>
       <c r="F8" t="n">
-        <v>4.6132</v>
+        <v>4.1091</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8689</v>
+        <v>2.3501</v>
       </c>
       <c r="H8" t="n">
-        <v>4.9304</v>
+        <v>4.1401</v>
       </c>
       <c r="I8" t="n">
-        <v>4.9765</v>
+        <v>4.1749</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8689</v>
+        <v>2.3501</v>
       </c>
       <c r="K8" t="n">
-        <v>394</v>
+        <v>264</v>
       </c>
       <c r="L8" t="n">
-        <v>118</v>
+        <v>199</v>
       </c>
       <c r="M8" t="n">
-        <v>6.8454</v>
+        <v>6.525</v>
       </c>
       <c r="N8" t="n">
-        <v>512</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.4691</v>
+        <v>6.4587</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2536</v>
+        <v>2.25</v>
       </c>
       <c r="D9" t="n">
-        <v>2.192</v>
+        <v>2.1292</v>
       </c>
       <c r="E9" t="n">
-        <v>6.4691</v>
+        <v>6.4587</v>
       </c>
       <c r="F9" t="n">
-        <v>4.119</v>
+        <v>4.5898</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3501</v>
+        <v>1.8689</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1556</v>
+        <v>4.8937</v>
       </c>
       <c r="I9" t="n">
-        <v>4.1749</v>
+        <v>4.9765</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3501</v>
+        <v>1.8689</v>
       </c>
       <c r="K9" t="n">
-        <v>264</v>
+        <v>394</v>
       </c>
       <c r="L9" t="n">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="M9" t="n">
-        <v>6.525</v>
+        <v>6.8454</v>
       </c>
       <c r="N9" t="n">
-        <v>463</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10">
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.0614</v>
+        <v>6.0469</v>
       </c>
       <c r="C10" t="n">
-        <v>2.1116</v>
+        <v>2.1065</v>
       </c>
       <c r="D10" t="n">
-        <v>2.0273</v>
+        <v>1.9652</v>
       </c>
       <c r="E10" t="n">
-        <v>6.0614</v>
+        <v>6.0469</v>
       </c>
       <c r="F10" t="n">
-        <v>3.8934</v>
+        <v>3.8789</v>
       </c>
       <c r="G10" t="n">
         <v>2.168</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8934</v>
+        <v>3.8789</v>
       </c>
       <c r="I10" t="n">
         <v>3.9115</v>
@@ -916,7 +916,7 @@
         <v>1.5477</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3733</v>
+        <v>1.326</v>
       </c>
       <c r="E11" t="n">
         <v>4.4426</v>
@@ -962,7 +962,7 @@
         <v>1.4947</v>
       </c>
       <c r="D12" t="n">
-        <v>1.3119</v>
+        <v>1.2655</v>
       </c>
       <c r="E12" t="n">
         <v>4.2906</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.0583</v>
+        <v>4.0565</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4138</v>
+        <v>1.4132</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2181</v>
+        <v>1.1722</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0583</v>
+        <v>4.0565</v>
       </c>
       <c r="F13" t="n">
-        <v>4.8027</v>
+        <v>4.0565</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7444</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.2275</v>
+        <v>4.0576</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2518</v>
+        <v>4.0576</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7444</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="L13" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.507400000000001</v>
+        <v>4.0576</v>
       </c>
       <c r="N13" t="n">
-        <v>309</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.0565</v>
+        <v>4.0458</v>
       </c>
       <c r="C14" t="n">
-        <v>1.4132</v>
+        <v>1.4094</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2174</v>
+        <v>1.1679</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0565</v>
+        <v>4.0458</v>
       </c>
       <c r="F14" t="n">
-        <v>4.0565</v>
+        <v>4.7902</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.7444</v>
       </c>
       <c r="H14" t="n">
-        <v>4.0576</v>
+        <v>5.208</v>
       </c>
       <c r="I14" t="n">
-        <v>4.0576</v>
+        <v>5.2518</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.7444</v>
       </c>
       <c r="K14" t="n">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M14" t="n">
-        <v>4.0576</v>
+        <v>4.507400000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>273</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15">
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.0078</v>
+        <v>3.9853</v>
       </c>
       <c r="C15" t="n">
-        <v>1.3962</v>
+        <v>1.3884</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1977</v>
+        <v>1.1438</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0078</v>
+        <v>3.9853</v>
       </c>
       <c r="F15" t="n">
-        <v>4.4862</v>
+        <v>4.4637</v>
       </c>
       <c r="G15" t="n">
         <v>-0.4784</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7313</v>
+        <v>4.696</v>
       </c>
       <c r="I15" t="n">
         <v>4.7754</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.9066</v>
+        <v>3.8827</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3609</v>
+        <v>1.3526</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1568</v>
+        <v>1.103</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9066</v>
+        <v>3.8827</v>
       </c>
       <c r="F16" t="n">
-        <v>3.216</v>
+        <v>3.1921</v>
       </c>
       <c r="G16" t="n">
         <v>0.6906</v>
       </c>
       <c r="H16" t="n">
-        <v>3.216</v>
+        <v>3.1921</v>
       </c>
       <c r="I16" t="n">
         <v>3.2461</v>
@@ -1192,7 +1192,7 @@
         <v>1.2742</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0562</v>
+        <v>1.0133</v>
       </c>
       <c r="E17" t="n">
         <v>3.6576</v>
@@ -1238,7 +1238,7 @@
         <v>1.2491</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0272</v>
+        <v>0.9846</v>
       </c>
       <c r="E18" t="n">
         <v>3.5857</v>
@@ -1284,7 +1284,7 @@
         <v>1.2413</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0181</v>
+        <v>0.9757</v>
       </c>
       <c r="E19" t="n">
         <v>3.5633</v>
@@ -1330,7 +1330,7 @@
         <v>1.1421</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9031</v>
+        <v>0.8622</v>
       </c>
       <c r="E20" t="n">
         <v>3.2785</v>
@@ -1376,7 +1376,7 @@
         <v>1.1116</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8677</v>
+        <v>0.8273</v>
       </c>
       <c r="E21" t="n">
         <v>3.1908</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.1818</v>
+        <v>3.1718</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1084</v>
+        <v>1.105</v>
       </c>
       <c r="D22" t="n">
-        <v>0.864</v>
+        <v>0.8197</v>
       </c>
       <c r="E22" t="n">
-        <v>3.1818</v>
+        <v>3.1718</v>
       </c>
       <c r="F22" t="n">
-        <v>2.6784</v>
+        <v>2.6684</v>
       </c>
       <c r="G22" t="n">
         <v>0.5034</v>
       </c>
       <c r="H22" t="n">
-        <v>2.6784</v>
+        <v>2.6684</v>
       </c>
       <c r="I22" t="n">
         <v>2.6909</v>
@@ -1468,7 +1468,7 @@
         <v>1.0973</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8511</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="E23" t="n">
         <v>3.1498</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.1269</v>
+        <v>3.1164</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0893</v>
+        <v>1.0857</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8418</v>
+        <v>0.7977</v>
       </c>
       <c r="E24" t="n">
-        <v>3.1269</v>
+        <v>3.1164</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8289</v>
+        <v>2.8184</v>
       </c>
       <c r="G24" t="n">
         <v>0.298</v>
       </c>
       <c r="H24" t="n">
-        <v>2.8289</v>
+        <v>2.8184</v>
       </c>
       <c r="I24" t="n">
         <v>2.8421</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.9871</v>
+        <v>2.9779</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0406</v>
+        <v>1.0374</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7854</v>
+        <v>0.7425</v>
       </c>
       <c r="E25" t="n">
-        <v>2.9871</v>
+        <v>2.9779</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4491</v>
+        <v>2.4399</v>
       </c>
       <c r="G25" t="n">
         <v>0.538</v>
       </c>
       <c r="H25" t="n">
-        <v>2.4491</v>
+        <v>2.4399</v>
       </c>
       <c r="I25" t="n">
         <v>2.4605</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.9842</v>
+        <v>2.9751</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0396</v>
+        <v>1.0364</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7842</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>2.9842</v>
+        <v>2.9751</v>
       </c>
       <c r="F26" t="n">
-        <v>2.4494</v>
+        <v>2.4403</v>
       </c>
       <c r="G26" t="n">
         <v>0.5348000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>2.4494</v>
+        <v>2.4403</v>
       </c>
       <c r="I26" t="n">
         <v>2.4608</v>
@@ -1652,7 +1652,7 @@
         <v>1.0016</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7401</v>
+        <v>0.7015</v>
       </c>
       <c r="E27" t="n">
         <v>2.875</v>
@@ -1698,7 +1698,7 @@
         <v>0.8877</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6081</v>
+        <v>0.5713</v>
       </c>
       <c r="E28" t="n">
         <v>2.5482</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.5085</v>
+        <v>2.4968</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8739</v>
+        <v>0.8698</v>
       </c>
       <c r="D29" t="n">
-        <v>0.592</v>
+        <v>0.5508</v>
       </c>
       <c r="E29" t="n">
-        <v>2.5085</v>
+        <v>2.4968</v>
       </c>
       <c r="F29" t="n">
-        <v>3.1234</v>
+        <v>3.1117</v>
       </c>
       <c r="G29" t="n">
         <v>-0.6149</v>
       </c>
       <c r="H29" t="n">
-        <v>3.1234</v>
+        <v>3.1117</v>
       </c>
       <c r="I29" t="n">
         <v>3.1379</v>
@@ -1790,7 +1790,7 @@
         <v>0.7621</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4624</v>
+        <v>0.4276</v>
       </c>
       <c r="E30" t="n">
         <v>2.1876</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.1785</v>
+        <v>2.1816</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7589</v>
+        <v>0.76</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4587</v>
+        <v>0.4252</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1785</v>
+        <v>2.1816</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8116</v>
+        <v>-0.8085</v>
       </c>
       <c r="G31" t="n">
         <v>2.9901</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8116</v>
+        <v>-0.8085</v>
       </c>
       <c r="I31" t="n">
         <v>-0.8154</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.0828</v>
+        <v>2.0725</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7256</v>
+        <v>0.722</v>
       </c>
       <c r="D32" t="n">
-        <v>0.42</v>
+        <v>0.3818</v>
       </c>
       <c r="E32" t="n">
-        <v>2.0828</v>
+        <v>2.0725</v>
       </c>
       <c r="F32" t="n">
-        <v>2.7568</v>
+        <v>2.7465</v>
       </c>
       <c r="G32" t="n">
         <v>-0.674</v>
       </c>
       <c r="H32" t="n">
-        <v>2.7568</v>
+        <v>2.7465</v>
       </c>
       <c r="I32" t="n">
         <v>2.7697</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.9001</v>
+        <v>1.8924</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6619</v>
+        <v>0.6593</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3462</v>
+        <v>0.31</v>
       </c>
       <c r="E33" t="n">
-        <v>1.9001</v>
+        <v>1.8924</v>
       </c>
       <c r="F33" t="n">
-        <v>2.0642</v>
+        <v>2.0565</v>
       </c>
       <c r="G33" t="n">
         <v>-0.1641</v>
       </c>
       <c r="H33" t="n">
-        <v>2.0642</v>
+        <v>2.0565</v>
       </c>
       <c r="I33" t="n">
         <v>2.0738</v>
@@ -1974,7 +1974,7 @@
         <v>0.6441</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3256</v>
+        <v>0.2927</v>
       </c>
       <c r="E34" t="n">
         <v>1.8489</v>
@@ -2020,7 +2020,7 @@
         <v>0.5896</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2623</v>
+        <v>0.2303</v>
       </c>
       <c r="E35" t="n">
         <v>1.6924</v>
@@ -2066,7 +2066,7 @@
         <v>0.5808</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2521</v>
+        <v>0.2203</v>
       </c>
       <c r="E36" t="n">
         <v>1.6672</v>
@@ -2112,7 +2112,7 @@
         <v>0.5582</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2259</v>
+        <v>0.1944</v>
       </c>
       <c r="E37" t="n">
         <v>1.6022</v>
@@ -2158,7 +2158,7 @@
         <v>0.4666</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1197</v>
+        <v>0.0897</v>
       </c>
       <c r="E38" t="n">
         <v>1.3393</v>
@@ -2204,7 +2204,7 @@
         <v>0.4509</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1015</v>
+        <v>0.0717</v>
       </c>
       <c r="E39" t="n">
         <v>1.2942</v>
@@ -2250,7 +2250,7 @@
         <v>0.4444</v>
       </c>
       <c r="D40" t="n">
-        <v>0.094</v>
+        <v>0.0643</v>
       </c>
       <c r="E40" t="n">
         <v>1.2757</v>
@@ -2296,7 +2296,7 @@
         <v>0.4249</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0713</v>
+        <v>0.042</v>
       </c>
       <c r="E41" t="n">
         <v>1.2196</v>
@@ -2342,7 +2342,7 @@
         <v>0.4062</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0497</v>
+        <v>0.0206</v>
       </c>
       <c r="E42" t="n">
         <v>1.166</v>
@@ -2388,7 +2388,7 @@
         <v>0.3892</v>
       </c>
       <c r="D43" t="n">
-        <v>0.03</v>
+        <v>0.0012</v>
       </c>
       <c r="E43" t="n">
         <v>1.1172</v>
@@ -2434,7 +2434,7 @@
         <v>0.3669</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0041</v>
+        <v>-0.0244</v>
       </c>
       <c r="E44" t="n">
         <v>1.0531</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.0215</v>
+        <v>1.0225</v>
       </c>
       <c r="C45" t="n">
-        <v>0.3559</v>
+        <v>0.3562</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0365</v>
       </c>
       <c r="E45" t="n">
-        <v>1.0215</v>
+        <v>1.0225</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.2594</v>
+        <v>-0.2584</v>
       </c>
       <c r="G45" t="n">
         <v>1.2809</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.2594</v>
+        <v>-0.2584</v>
       </c>
       <c r="I45" t="n">
         <v>-0.2606</v>
@@ -2526,7 +2526,7 @@
         <v>0.3389</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0284</v>
+        <v>-0.0564</v>
       </c>
       <c r="E46" t="n">
         <v>0.9727</v>
@@ -2572,7 +2572,7 @@
         <v>0.3083</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.0639</v>
+        <v>-0.0914</v>
       </c>
       <c r="E47" t="n">
         <v>0.8849</v>
@@ -2618,7 +2618,7 @@
         <v>0.2208</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.1653</v>
+        <v>-0.1914</v>
       </c>
       <c r="E48" t="n">
         <v>0.6338</v>
@@ -2664,7 +2664,7 @@
         <v>0.1492</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2483</v>
+        <v>-0.2733</v>
       </c>
       <c r="E49" t="n">
         <v>0.4283</v>
@@ -2710,7 +2710,7 @@
         <v>0.1286</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2723</v>
+        <v>-0.2969</v>
       </c>
       <c r="E50" t="n">
         <v>0.3691</v>
@@ -2756,7 +2756,7 @@
         <v>0.1258</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2755</v>
+        <v>-0.3</v>
       </c>
       <c r="E51" t="n">
         <v>0.3611</v>
@@ -2802,7 +2802,7 @@
         <v>0.1087</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2954</v>
+        <v>-0.3196</v>
       </c>
       <c r="E52" t="n">
         <v>0.3119</v>
@@ -2848,7 +2848,7 @@
         <v>0.1019</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3032</v>
+        <v>-0.3274</v>
       </c>
       <c r="E53" t="n">
         <v>0.2924</v>
@@ -2894,7 +2894,7 @@
         <v>0.0515</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3617</v>
+        <v>-0.385</v>
       </c>
       <c r="E54" t="n">
         <v>0.1478</v>
@@ -2940,7 +2940,7 @@
         <v>0.0204</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.3976</v>
+        <v>-0.4205</v>
       </c>
       <c r="E55" t="n">
         <v>0.0587</v>
@@ -2986,7 +2986,7 @@
         <v>-0.0328</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4594</v>
+        <v>-0.4814</v>
       </c>
       <c r="E56" t="n">
         <v>-0.09420000000000001</v>
@@ -3032,7 +3032,7 @@
         <v>-0.0828</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5173</v>
+        <v>-0.5386</v>
       </c>
       <c r="E57" t="n">
         <v>-0.2376</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.2635</v>
+        <v>-0.2628</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.0916</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5278</v>
+        <v>-0.5486</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.2635</v>
+        <v>-0.2628</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.2052</v>
+        <v>-0.2045</v>
       </c>
       <c r="G58" t="n">
         <v>-0.0583</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.2052</v>
+        <v>-0.2045</v>
       </c>
       <c r="I58" t="n">
         <v>-0.2062</v>
@@ -3124,7 +3124,7 @@
         <v>-0.198</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.651</v>
+        <v>-0.6704</v>
       </c>
       <c r="E59" t="n">
         <v>-0.5684</v>
@@ -3170,7 +3170,7 @@
         <v>-0.2169</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6728</v>
+        <v>-0.6919</v>
       </c>
       <c r="E60" t="n">
         <v>-0.6225000000000001</v>
@@ -3216,7 +3216,7 @@
         <v>-0.2187</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.675</v>
+        <v>-0.694</v>
       </c>
       <c r="E61" t="n">
         <v>-0.6278</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.6414</v>
+        <v>-0.6405999999999999</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2234</v>
+        <v>-0.2232</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6805</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.6414</v>
+        <v>-0.6405999999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.2088</v>
+        <v>-0.208</v>
       </c>
       <c r="G62" t="n">
         <v>-0.4326</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.2088</v>
+        <v>-0.208</v>
       </c>
       <c r="I62" t="n">
         <v>-0.2098</v>
@@ -3308,7 +3308,7 @@
         <v>-0.2563</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7185</v>
+        <v>-0.737</v>
       </c>
       <c r="E63" t="n">
         <v>-0.7356</v>
@@ -3354,7 +3354,7 @@
         <v>-0.2763</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7418</v>
+        <v>-0.7599</v>
       </c>
       <c r="E64" t="n">
         <v>-0.7932</v>
@@ -3400,7 +3400,7 @@
         <v>-0.3375</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8127</v>
+        <v>-0.8299</v>
       </c>
       <c r="E65" t="n">
         <v>-0.9688</v>
@@ -3446,7 +3446,7 @@
         <v>-0.3828</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8653</v>
+        <v>-0.8817</v>
       </c>
       <c r="E66" t="n">
         <v>-1.0988</v>
@@ -3492,7 +3492,7 @@
         <v>-0.4143</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9018</v>
+        <v>-0.9177</v>
       </c>
       <c r="E67" t="n">
         <v>-1.1892</v>
@@ -3538,7 +3538,7 @@
         <v>-0.5057</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.0078</v>
+        <v>-1.0223</v>
       </c>
       <c r="E68" t="n">
         <v>-1.4517</v>
@@ -3584,7 +3584,7 @@
         <v>-0.5978</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.1146</v>
+        <v>-1.1276</v>
       </c>
       <c r="E69" t="n">
         <v>-1.716</v>
@@ -3630,7 +3630,7 @@
         <v>-0.6002</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.1174</v>
+        <v>-1.1304</v>
       </c>
       <c r="E70" t="n">
         <v>-1.723</v>
@@ -3676,7 +3676,7 @@
         <v>-0.7353</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.274</v>
+        <v>-1.2848</v>
       </c>
       <c r="E71" t="n">
         <v>-2.1106</v>
@@ -3722,7 +3722,7 @@
         <v>-0.7567</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.2988</v>
+        <v>-1.3092</v>
       </c>
       <c r="E72" t="n">
         <v>-2.172</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-2.2645</v>
+        <v>-2.2578</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.7889</v>
+        <v>-0.7865</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.3362</v>
+        <v>-1.3434</v>
       </c>
       <c r="E73" t="n">
-        <v>-2.2645</v>
+        <v>-2.2578</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.7892</v>
+        <v>-1.7825</v>
       </c>
       <c r="G73" t="n">
         <v>-0.4753</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.7892</v>
+        <v>-1.7825</v>
       </c>
       <c r="I73" t="n">
         <v>-1.7975</v>
@@ -3814,7 +3814,7 @@
         <v>-0.8351</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.3897</v>
+        <v>-1.3989</v>
       </c>
       <c r="E74" t="n">
         <v>-2.3971</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-2.6647</v>
+        <v>-2.6575</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.9283</v>
+        <v>-0.9258</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.4978</v>
+        <v>-1.5027</v>
       </c>
       <c r="E75" t="n">
-        <v>-2.6647</v>
+        <v>-2.6575</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.9329</v>
+        <v>-1.9257</v>
       </c>
       <c r="G75" t="n">
         <v>-0.7318</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.9329</v>
+        <v>-1.9257</v>
       </c>
       <c r="I75" t="n">
         <v>-1.9419</v>
@@ -3906,7 +3906,7 @@
         <v>-0.9844000000000001</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.5629</v>
+        <v>-1.5697</v>
       </c>
       <c r="E76" t="n">
         <v>-2.8258</v>
@@ -3952,7 +3952,7 @@
         <v>-1.003</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.5844</v>
+        <v>-1.5909</v>
       </c>
       <c r="E77" t="n">
         <v>-2.879</v>
@@ -3998,7 +3998,7 @@
         <v>-1.035</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.6216</v>
+        <v>-1.6276</v>
       </c>
       <c r="E78" t="n">
         <v>-2.9711</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-3.4695</v>
+        <v>-3.4618</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.2087</v>
+        <v>-1.206</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.823</v>
+        <v>-1.8231</v>
       </c>
       <c r="E79" t="n">
-        <v>-3.4695</v>
+        <v>-3.4618</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.0778</v>
+        <v>-2.0701</v>
       </c>
       <c r="G79" t="n">
         <v>-1.3917</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.0778</v>
+        <v>-2.0701</v>
       </c>
       <c r="I79" t="n">
         <v>-2.0875</v>
@@ -4090,7 +4090,7 @@
         <v>-1.7036</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.3969</v>
+        <v>-2.3922</v>
       </c>
       <c r="E80" t="n">
         <v>-4.8902</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-6.3407</v>
+        <v>-6.3023</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.2089</v>
+        <v>-2.1955</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.9829</v>
+        <v>-2.9547</v>
       </c>
       <c r="E81" t="n">
-        <v>-6.3407</v>
+        <v>-6.3023</v>
       </c>
       <c r="F81" t="n">
-        <v>-5.157</v>
+        <v>-5.1186</v>
       </c>
       <c r="G81" t="n">
         <v>-1.1837</v>
       </c>
       <c r="H81" t="n">
-        <v>-5.157</v>
+        <v>-5.1186</v>
       </c>
       <c r="I81" t="n">
         <v>-5.2052</v>

--- a/database/event/8043/event_8043_evp_summary.xlsx
+++ b/database/event/8043/event_8043_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.593</v>
+        <v>9.975199999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3419</v>
+        <v>3.475</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7427</v>
+        <v>3.8419</v>
       </c>
       <c r="E2" t="n">
-        <v>9.593</v>
+        <v>9.975199999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2338</v>
+        <v>4.2281</v>
       </c>
       <c r="G2" t="n">
-        <v>5.3592</v>
+        <v>5.3213</v>
       </c>
       <c r="H2" t="n">
-        <v>6.5415</v>
+        <v>6.5292</v>
       </c>
       <c r="I2" t="n">
-        <v>6.7101</v>
+        <v>6.6974</v>
       </c>
       <c r="J2" t="n">
-        <v>5.3592</v>
+        <v>5.3213</v>
       </c>
       <c r="K2" t="n">
         <v>238</v>
@@ -529,7 +529,7 @@
         <v>189</v>
       </c>
       <c r="M2" t="n">
-        <v>12.0693</v>
+        <v>12.0187</v>
       </c>
       <c r="N2" t="n">
         <v>427</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.0171</v>
+        <v>7.3304</v>
       </c>
       <c r="C3" t="n">
-        <v>2.4445</v>
+        <v>2.5537</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5701</v>
+        <v>2.6605</v>
       </c>
       <c r="E3" t="n">
-        <v>7.0171</v>
+        <v>7.3304</v>
       </c>
       <c r="F3" t="n">
-        <v>3.226</v>
+        <v>3.2264</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7911</v>
+        <v>3.8277</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3359</v>
+        <v>4.3366</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4476</v>
+        <v>4.4484</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7911</v>
+        <v>3.8277</v>
       </c>
       <c r="K3" t="n">
         <v>264</v>
@@ -575,7 +575,7 @@
         <v>199</v>
       </c>
       <c r="M3" t="n">
-        <v>8.238700000000001</v>
+        <v>8.2761</v>
       </c>
       <c r="N3" t="n">
         <v>463</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3261</v>
+        <v>6.4164</v>
       </c>
       <c r="C4" t="n">
-        <v>2.2038</v>
+        <v>2.2353</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2556</v>
+        <v>2.2522</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3261</v>
+        <v>6.4164</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7601</v>
+        <v>2.7604</v>
       </c>
       <c r="G4" t="n">
-        <v>3.566</v>
+        <v>3.5772</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3161</v>
+        <v>3.3166</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4016</v>
+        <v>3.4021</v>
       </c>
       <c r="J4" t="n">
-        <v>3.566</v>
+        <v>3.5772</v>
       </c>
       <c r="K4" t="n">
         <v>264</v>
@@ -621,7 +621,7 @@
         <v>199</v>
       </c>
       <c r="M4" t="n">
-        <v>6.9676</v>
+        <v>6.9793</v>
       </c>
       <c r="N4" t="n">
         <v>463</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.1169</v>
+        <v>6.3769</v>
       </c>
       <c r="C5" t="n">
-        <v>2.1309</v>
+        <v>2.2215</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1603</v>
+        <v>2.2346</v>
       </c>
       <c r="E5" t="n">
-        <v>6.1169</v>
+        <v>6.3769</v>
       </c>
       <c r="F5" t="n">
         <v>4.6771</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4398</v>
+        <v>1.4396</v>
       </c>
       <c r="H5" t="n">
         <v>7.5118</v>
@@ -658,7 +658,7 @@
         <v>7.5118</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4398</v>
+        <v>1.4396</v>
       </c>
       <c r="K5" t="n">
         <v>241</v>
@@ -667,7 +667,7 @@
         <v>82</v>
       </c>
       <c r="M5" t="n">
-        <v>8.951599999999999</v>
+        <v>8.9514</v>
       </c>
       <c r="N5" t="n">
         <v>323</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.8652</v>
+        <v>6.102</v>
       </c>
       <c r="C6" t="n">
-        <v>2.0432</v>
+        <v>2.1257</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0458</v>
+        <v>2.1118</v>
       </c>
       <c r="E6" t="n">
-        <v>5.8652</v>
+        <v>6.102</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5131</v>
+        <v>3.783</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3521</v>
+        <v>2.0464</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9642</v>
+        <v>5.5549</v>
       </c>
       <c r="I6" t="n">
-        <v>5.0921</v>
+        <v>5.8449</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3521</v>
+        <v>2.0464</v>
       </c>
       <c r="K6" t="n">
-        <v>264</v>
+        <v>394</v>
       </c>
       <c r="L6" t="n">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="M6" t="n">
-        <v>7.4442</v>
+        <v>7.8913</v>
       </c>
       <c r="N6" t="n">
-        <v>463</v>
+        <v>512</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.8296</v>
+        <v>5.8977</v>
       </c>
       <c r="C7" t="n">
-        <v>2.0308</v>
+        <v>2.0546</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0296</v>
+        <v>2.0206</v>
       </c>
       <c r="E7" t="n">
-        <v>5.8296</v>
+        <v>5.8977</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7832</v>
+        <v>3.5048</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0464</v>
+        <v>2.3509</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5553</v>
+        <v>4.946</v>
       </c>
       <c r="I7" t="n">
-        <v>5.8452</v>
+        <v>5.0735</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0464</v>
+        <v>2.3509</v>
       </c>
       <c r="K7" t="n">
-        <v>394</v>
+        <v>264</v>
       </c>
       <c r="L7" t="n">
-        <v>118</v>
+        <v>199</v>
       </c>
       <c r="M7" t="n">
-        <v>7.8916</v>
+        <v>7.4244</v>
       </c>
       <c r="N7" t="n">
-        <v>512</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.7953</v>
+        <v>5.8672</v>
       </c>
       <c r="C8" t="n">
-        <v>2.0189</v>
+        <v>2.0439</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0139</v>
+        <v>2.0069</v>
       </c>
       <c r="E8" t="n">
-        <v>5.7953</v>
+        <v>5.8672</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5759</v>
+        <v>3.5762</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2194</v>
+        <v>2.2387</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1015</v>
+        <v>5.1022</v>
       </c>
       <c r="I8" t="n">
-        <v>5.233</v>
+        <v>5.2337</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2194</v>
+        <v>2.2387</v>
       </c>
       <c r="K8" t="n">
         <v>264</v>
@@ -805,7 +805,7 @@
         <v>199</v>
       </c>
       <c r="M8" t="n">
-        <v>7.452399999999999</v>
+        <v>7.4724</v>
       </c>
       <c r="N8" t="n">
         <v>463</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.3167</v>
+        <v>5.3742</v>
       </c>
       <c r="C9" t="n">
-        <v>1.8522</v>
+        <v>1.8722</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7961</v>
+        <v>1.7867</v>
       </c>
       <c r="E9" t="n">
-        <v>5.3167</v>
+        <v>5.3742</v>
       </c>
       <c r="F9" t="n">
         <v>3.4695</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.1614</v>
+        <v>5.2638</v>
       </c>
       <c r="C10" t="n">
-        <v>1.7981</v>
+        <v>1.8337</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7254</v>
+        <v>1.7374</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1614</v>
+        <v>5.2638</v>
       </c>
       <c r="F10" t="n">
-        <v>3.5905</v>
+        <v>3.5907</v>
       </c>
       <c r="G10" t="n">
         <v>1.5709</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1335</v>
+        <v>5.1339</v>
       </c>
       <c r="I10" t="n">
-        <v>5.4014</v>
+        <v>5.4019</v>
       </c>
       <c r="J10" t="n">
         <v>1.5709</v>
@@ -897,7 +897,7 @@
         <v>118</v>
       </c>
       <c r="M10" t="n">
-        <v>6.9723</v>
+        <v>6.9728</v>
       </c>
       <c r="N10" t="n">
         <v>512</v>
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.2659</v>
+        <v>4.267</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4861</v>
+        <v>1.4865</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3177</v>
+        <v>1.2922</v>
       </c>
       <c r="E11" t="n">
-        <v>4.2659</v>
+        <v>4.267</v>
       </c>
       <c r="F11" t="n">
         <v>2.738</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5278</v>
+        <v>1.5156</v>
       </c>
       <c r="H11" t="n">
         <v>3.2678</v>
@@ -934,7 +934,7 @@
         <v>3.2678</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5278</v>
+        <v>1.5156</v>
       </c>
       <c r="K11" t="n">
         <v>241</v>
@@ -943,7 +943,7 @@
         <v>82</v>
       </c>
       <c r="M11" t="n">
-        <v>4.7956</v>
+        <v>4.7834</v>
       </c>
       <c r="N11" t="n">
         <v>323</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.8524</v>
+        <v>4.2313</v>
       </c>
       <c r="C12" t="n">
-        <v>1.3421</v>
+        <v>1.4741</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1295</v>
+        <v>1.2762</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8524</v>
+        <v>4.2313</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8663</v>
+        <v>3.8574</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0139</v>
+        <v>-0.0055</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7371</v>
+        <v>5.7177</v>
       </c>
       <c r="I12" t="n">
-        <v>5.7371</v>
+        <v>5.7177</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0139</v>
+        <v>-0.0055</v>
       </c>
       <c r="K12" t="n">
         <v>252</v>
@@ -989,7 +989,7 @@
         <v>39</v>
       </c>
       <c r="M12" t="n">
-        <v>5.7232</v>
+        <v>5.7122</v>
       </c>
       <c r="N12" t="n">
         <v>291</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.8011</v>
+        <v>3.9654</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3242</v>
+        <v>1.3814</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1061</v>
+        <v>1.1574</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8011</v>
+        <v>3.9654</v>
       </c>
       <c r="F13" t="n">
-        <v>4.3011</v>
+        <v>3.0058</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5</v>
+        <v>0.7584</v>
       </c>
       <c r="H13" t="n">
-        <v>6.6888</v>
+        <v>3.8538</v>
       </c>
       <c r="I13" t="n">
-        <v>6.8612</v>
+        <v>3.9531</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5</v>
+        <v>0.7584</v>
       </c>
       <c r="K13" t="n">
-        <v>261</v>
+        <v>203</v>
       </c>
       <c r="L13" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="M13" t="n">
-        <v>6.3612</v>
+        <v>4.7115</v>
       </c>
       <c r="N13" t="n">
-        <v>309</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.7519</v>
+        <v>3.9094</v>
       </c>
       <c r="C14" t="n">
-        <v>1.307</v>
+        <v>1.3619</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0837</v>
+        <v>1.1324</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7519</v>
+        <v>3.9094</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0042</v>
+        <v>4.3087</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7477</v>
+        <v>-0.5</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8503</v>
+        <v>6.7055</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9495</v>
+        <v>6.8783</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7477</v>
+        <v>-0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>203</v>
+        <v>261</v>
       </c>
       <c r="L14" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6972</v>
+        <v>6.3783</v>
       </c>
       <c r="N14" t="n">
-        <v>267</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.7146</v>
+        <v>3.8732</v>
       </c>
       <c r="C15" t="n">
-        <v>1.294</v>
+        <v>1.3493</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0668</v>
+        <v>1.1163</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7146</v>
+        <v>3.8732</v>
       </c>
       <c r="F15" t="n">
-        <v>3.7146</v>
+        <v>3.7326</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4051</v>
+        <v>5.4445</v>
       </c>
       <c r="I15" t="n">
-        <v>5.4051</v>
+        <v>5.4445</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.4051</v>
+        <v>5.4445</v>
       </c>
       <c r="N15" t="n">
         <v>270</v>
@@ -1136,599 +1136,599 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.6791</v>
+        <v>3.8281</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2817</v>
+        <v>1.3336</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0506</v>
+        <v>1.0961</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6791</v>
+        <v>3.8281</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8576</v>
+        <v>3.4502</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8215</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5294</v>
+        <v>4.8264</v>
       </c>
       <c r="I16" t="n">
-        <v>3.7136</v>
+        <v>4.8264</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8215</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>394</v>
+        <v>220</v>
       </c>
       <c r="L16" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5351</v>
+        <v>4.8264</v>
       </c>
       <c r="N16" t="n">
-        <v>512</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.4326</v>
+        <v>3.8195</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1958</v>
+        <v>1.3306</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9384</v>
+        <v>1.0923</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4326</v>
+        <v>3.8195</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4326</v>
+        <v>2.8577</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.8215</v>
       </c>
       <c r="H17" t="n">
-        <v>4.788</v>
+        <v>3.5297</v>
       </c>
       <c r="I17" t="n">
-        <v>4.788</v>
+        <v>3.714</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.8215</v>
       </c>
       <c r="K17" t="n">
-        <v>220</v>
+        <v>394</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="M17" t="n">
-        <v>4.788</v>
+        <v>4.5355</v>
       </c>
       <c r="N17" t="n">
-        <v>220</v>
+        <v>512</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.3803</v>
+        <v>3.5584</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1776</v>
+        <v>1.2396</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9146</v>
+        <v>0.9756</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3803</v>
+        <v>3.5584</v>
       </c>
       <c r="F18" t="n">
-        <v>3.3803</v>
+        <v>3.1321</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6735</v>
+        <v>4.1303</v>
       </c>
       <c r="I18" t="n">
-        <v>4.6735</v>
+        <v>4.1303</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>273</v>
+        <v>215</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6735</v>
+        <v>4.1303</v>
       </c>
       <c r="N18" t="n">
-        <v>273</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.3161</v>
+        <v>3.5154</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1552</v>
+        <v>1.2247</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8854</v>
+        <v>0.9564</v>
       </c>
       <c r="E19" t="n">
-        <v>3.3161</v>
+        <v>3.5154</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7263</v>
+        <v>3.3878</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5898</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2421</v>
+        <v>4.6898</v>
       </c>
       <c r="I19" t="n">
-        <v>3.3256</v>
+        <v>4.6898</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5898</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>203</v>
+        <v>273</v>
       </c>
       <c r="L19" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9154</v>
+        <v>4.6898</v>
       </c>
       <c r="N19" t="n">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.3143</v>
+        <v>3.3942</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1546</v>
+        <v>1.1824</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8845</v>
+        <v>0.9023</v>
       </c>
       <c r="E20" t="n">
-        <v>3.3143</v>
+        <v>3.3942</v>
       </c>
       <c r="F20" t="n">
-        <v>3.3354</v>
+        <v>2.7306</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0211</v>
+        <v>0.5897</v>
       </c>
       <c r="H20" t="n">
-        <v>4.5753</v>
+        <v>3.2515</v>
       </c>
       <c r="I20" t="n">
-        <v>4.6932</v>
+        <v>3.3353</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0211</v>
+        <v>0.5897</v>
       </c>
       <c r="K20" t="n">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="L20" t="n">
-        <v>189</v>
+        <v>64</v>
       </c>
       <c r="M20" t="n">
-        <v>4.6721</v>
+        <v>3.925</v>
       </c>
       <c r="N20" t="n">
-        <v>427</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.2949</v>
+        <v>3.3709</v>
       </c>
       <c r="C21" t="n">
-        <v>1.1478</v>
+        <v>1.1743</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8757</v>
+        <v>0.8919</v>
       </c>
       <c r="E21" t="n">
-        <v>3.2949</v>
+        <v>3.3709</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5906</v>
+        <v>2.7094</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7043</v>
+        <v>0.529</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9451</v>
+        <v>3.2051</v>
       </c>
       <c r="I21" t="n">
-        <v>3.021</v>
+        <v>3.2877</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7043</v>
+        <v>0.529</v>
       </c>
       <c r="K21" t="n">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="L21" t="n">
-        <v>189</v>
+        <v>64</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7253</v>
+        <v>3.8167</v>
       </c>
       <c r="N21" t="n">
-        <v>427</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Shr</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.2805</v>
+        <v>3.3372</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1428</v>
+        <v>1.1626</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8691</v>
+        <v>0.8768</v>
       </c>
       <c r="E22" t="n">
-        <v>3.2805</v>
+        <v>3.3372</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3812</v>
+        <v>3.1069</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8993</v>
+        <v>0.0877</v>
       </c>
       <c r="H22" t="n">
-        <v>2.4867</v>
+        <v>4.075</v>
       </c>
       <c r="I22" t="n">
-        <v>2.4867</v>
+        <v>4.075</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8993</v>
+        <v>0.0877</v>
       </c>
       <c r="K22" t="n">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="L22" t="n">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="M22" t="n">
-        <v>3.386</v>
+        <v>4.1627</v>
       </c>
       <c r="N22" t="n">
-        <v>323</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.2306</v>
+        <v>3.3314</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1254</v>
+        <v>1.1606</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8464</v>
+        <v>0.8742</v>
       </c>
       <c r="E23" t="n">
-        <v>3.2306</v>
+        <v>3.3314</v>
       </c>
       <c r="F23" t="n">
-        <v>2.7014</v>
+        <v>2.3812</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5292</v>
+        <v>0.9266</v>
       </c>
       <c r="H23" t="n">
-        <v>3.1877</v>
+        <v>2.4867</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2698</v>
+        <v>2.4867</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5292</v>
+        <v>0.9266</v>
       </c>
       <c r="K23" t="n">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="L23" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="M23" t="n">
-        <v>3.799</v>
+        <v>3.4133</v>
       </c>
       <c r="N23" t="n">
-        <v>267</v>
+        <v>323</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.2092</v>
+        <v>3.3188</v>
       </c>
       <c r="C24" t="n">
-        <v>1.118</v>
+        <v>1.1562</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8367</v>
+        <v>0.8686</v>
       </c>
       <c r="E24" t="n">
-        <v>3.2092</v>
+        <v>3.3188</v>
       </c>
       <c r="F24" t="n">
-        <v>3.671</v>
+        <v>3.1086</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4618</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>5.3097</v>
+        <v>4.0788</v>
       </c>
       <c r="I24" t="n">
-        <v>5.5868</v>
+        <v>4.0788</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4618</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>394</v>
+        <v>238</v>
       </c>
       <c r="L24" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>5.125</v>
+        <v>4.0788</v>
       </c>
       <c r="N24" t="n">
-        <v>512</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shr</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.1947</v>
+        <v>3.3098</v>
       </c>
       <c r="C25" t="n">
-        <v>1.1129</v>
+        <v>1.153</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.8646</v>
       </c>
       <c r="E25" t="n">
-        <v>3.1947</v>
+        <v>3.3098</v>
       </c>
       <c r="F25" t="n">
-        <v>3.1066</v>
+        <v>2.595</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0881</v>
+        <v>0.6902</v>
       </c>
       <c r="H25" t="n">
-        <v>4.0744</v>
+        <v>2.9547</v>
       </c>
       <c r="I25" t="n">
-        <v>4.0744</v>
+        <v>3.0308</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0881</v>
+        <v>0.6902</v>
       </c>
       <c r="K25" t="n">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="L25" t="n">
-        <v>39</v>
+        <v>189</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1625</v>
+        <v>3.721</v>
       </c>
       <c r="N25" t="n">
-        <v>291</v>
+        <v>427</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.1427</v>
+        <v>3.2753</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0948</v>
+        <v>1.141</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8064</v>
+        <v>0.8492</v>
       </c>
       <c r="E26" t="n">
-        <v>3.1427</v>
+        <v>3.2753</v>
       </c>
       <c r="F26" t="n">
-        <v>3.1427</v>
+        <v>3.5167</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.5195</v>
       </c>
       <c r="H26" t="n">
-        <v>4.1534</v>
+        <v>4.972</v>
       </c>
       <c r="I26" t="n">
-        <v>4.1534</v>
+        <v>4.972</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.5195</v>
       </c>
       <c r="K26" t="n">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M26" t="n">
-        <v>4.1534</v>
+        <v>4.452500000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>215</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.1083</v>
+        <v>3.192</v>
       </c>
       <c r="C27" t="n">
-        <v>1.0828</v>
+        <v>1.112</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>3.1083</v>
+        <v>3.192</v>
       </c>
       <c r="F27" t="n">
-        <v>3.1083</v>
+        <v>3.6698</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.4618</v>
       </c>
       <c r="H27" t="n">
-        <v>4.0782</v>
+        <v>5.3072</v>
       </c>
       <c r="I27" t="n">
-        <v>4.0782</v>
+        <v>5.5842</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.4618</v>
       </c>
       <c r="K27" t="n">
-        <v>238</v>
+        <v>394</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="M27" t="n">
-        <v>4.0782</v>
+        <v>5.1224</v>
       </c>
       <c r="N27" t="n">
-        <v>238</v>
+        <v>512</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.9971</v>
+        <v>3.1794</v>
       </c>
       <c r="C28" t="n">
-        <v>1.0441</v>
+        <v>1.1076</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7401</v>
+        <v>0.8063</v>
       </c>
       <c r="E28" t="n">
-        <v>2.9971</v>
+        <v>3.1794</v>
       </c>
       <c r="F28" t="n">
-        <v>3.5166</v>
+        <v>3.3355</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.5195</v>
+        <v>-0.0594</v>
       </c>
       <c r="H28" t="n">
-        <v>4.9717</v>
+        <v>4.5755</v>
       </c>
       <c r="I28" t="n">
-        <v>4.9717</v>
+        <v>4.6934</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.5195</v>
+        <v>-0.0594</v>
       </c>
       <c r="K28" t="n">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="L28" t="n">
-        <v>49</v>
+        <v>189</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4522</v>
+        <v>4.633999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>227</v>
+        <v>427</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.8549</v>
+        <v>2.8016</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9946</v>
+        <v>0.976</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6754</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>2.8549</v>
+        <v>2.8016</v>
       </c>
       <c r="F29" t="n">
-        <v>2.8549</v>
+        <v>2.8605</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3.5235</v>
+        <v>3.5359</v>
       </c>
       <c r="I29" t="n">
-        <v>3.5235</v>
+        <v>3.5359</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5235</v>
+        <v>3.5359</v>
       </c>
       <c r="N29" t="n">
         <v>270</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.8056</v>
+        <v>2.7784</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9774</v>
+        <v>0.9679</v>
       </c>
       <c r="D30" t="n">
-        <v>0.653</v>
+        <v>0.6272</v>
       </c>
       <c r="E30" t="n">
-        <v>2.8056</v>
+        <v>2.7784</v>
       </c>
       <c r="F30" t="n">
-        <v>2.8037</v>
+        <v>2.7804</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0019</v>
+        <v>0.0017</v>
       </c>
       <c r="H30" t="n">
-        <v>3.4114</v>
+        <v>3.3605</v>
       </c>
       <c r="I30" t="n">
-        <v>3.4993</v>
+        <v>3.4471</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0019</v>
+        <v>0.0017</v>
       </c>
       <c r="K30" t="n">
         <v>203</v>
@@ -1817,7 +1817,7 @@
         <v>64</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5012</v>
+        <v>3.4488</v>
       </c>
       <c r="N30" t="n">
         <v>267</v>
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.5467</v>
+        <v>2.7681</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8872</v>
+        <v>0.9643</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5351</v>
+        <v>0.6226</v>
       </c>
       <c r="E31" t="n">
-        <v>2.5467</v>
+        <v>2.7681</v>
       </c>
       <c r="F31" t="n">
         <v>2.5467</v>
@@ -1872,216 +1872,216 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.4573</v>
+        <v>2.5248</v>
       </c>
       <c r="C32" t="n">
-        <v>0.856</v>
+        <v>0.8796</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4944</v>
+        <v>0.514</v>
       </c>
       <c r="E32" t="n">
-        <v>2.4573</v>
+        <v>2.5248</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2872</v>
+        <v>2.3533</v>
       </c>
       <c r="G32" t="n">
-        <v>2.7445</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2872</v>
+        <v>2.4258</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2946</v>
+        <v>2.4258</v>
       </c>
       <c r="J32" t="n">
-        <v>2.7445</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="L32" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.4499</v>
+        <v>2.4258</v>
       </c>
       <c r="N32" t="n">
-        <v>427</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>nicx</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.3505</v>
+        <v>2.4812</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8188</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4458</v>
+        <v>0.4945</v>
       </c>
       <c r="E33" t="n">
-        <v>2.3505</v>
+        <v>2.4812</v>
       </c>
       <c r="F33" t="n">
-        <v>2.3505</v>
+        <v>2.3451</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.4195</v>
+        <v>2.4077</v>
       </c>
       <c r="I33" t="n">
-        <v>2.4195</v>
+        <v>2.4077</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>220</v>
+        <v>168</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2.4195</v>
+        <v>2.4077</v>
       </c>
       <c r="N33" t="n">
-        <v>220</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>nicx</t>
+          <t>hyped</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.3447</v>
+        <v>2.4529</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8168</v>
+        <v>0.8545</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4432</v>
+        <v>0.4818</v>
       </c>
       <c r="E34" t="n">
-        <v>2.3447</v>
+        <v>2.4529</v>
       </c>
       <c r="F34" t="n">
-        <v>2.3447</v>
+        <v>2.3319</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.4068</v>
+        <v>2.3788</v>
       </c>
       <c r="I34" t="n">
-        <v>2.4068</v>
+        <v>2.3788</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>168</v>
+        <v>238</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.4068</v>
+        <v>2.3788</v>
       </c>
       <c r="N34" t="n">
-        <v>168</v>
+        <v>238</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.3366</v>
+        <v>2.3854</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.831</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4395</v>
+        <v>0.4517</v>
       </c>
       <c r="E35" t="n">
-        <v>2.3366</v>
+        <v>2.3854</v>
       </c>
       <c r="F35" t="n">
-        <v>2.3435</v>
+        <v>2.2942</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0069</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.4042</v>
+        <v>2.2964</v>
       </c>
       <c r="I35" t="n">
-        <v>2.4042</v>
+        <v>2.2964</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.0069</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>178</v>
+        <v>270</v>
       </c>
       <c r="L35" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.3973</v>
+        <v>2.2964</v>
       </c>
       <c r="N35" t="n">
-        <v>227</v>
+        <v>270</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>hyped</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.3318</v>
+        <v>2.3715</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8123</v>
+        <v>0.8262</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4373</v>
+        <v>0.4455</v>
       </c>
       <c r="E36" t="n">
-        <v>2.3318</v>
+        <v>2.3715</v>
       </c>
       <c r="F36" t="n">
-        <v>2.3318</v>
+        <v>2.3299</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2.3787</v>
+        <v>2.3745</v>
       </c>
       <c r="I36" t="n">
-        <v>2.3787</v>
+        <v>2.3745</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.3787</v>
+        <v>2.3745</v>
       </c>
       <c r="N36" t="n">
         <v>238</v>
@@ -2102,139 +2102,139 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.3298</v>
+        <v>2.3624</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8116</v>
+        <v>0.823</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4364</v>
+        <v>0.4414</v>
       </c>
       <c r="E37" t="n">
-        <v>2.3298</v>
+        <v>2.3624</v>
       </c>
       <c r="F37" t="n">
-        <v>2.3298</v>
+        <v>-0.2871</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2.7062</v>
       </c>
       <c r="H37" t="n">
-        <v>2.3743</v>
+        <v>-0.2871</v>
       </c>
       <c r="I37" t="n">
-        <v>2.3743</v>
+        <v>-0.2945</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>2.7062</v>
       </c>
       <c r="K37" t="n">
         <v>238</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="M37" t="n">
-        <v>2.3743</v>
+        <v>2.4117</v>
       </c>
       <c r="N37" t="n">
-        <v>238</v>
+        <v>427</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.275</v>
+        <v>2.2655</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7925</v>
+        <v>0.7892</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4114</v>
+        <v>0.3981</v>
       </c>
       <c r="E38" t="n">
-        <v>2.275</v>
+        <v>2.2655</v>
       </c>
       <c r="F38" t="n">
-        <v>2.275</v>
+        <v>2.5887</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.4591</v>
       </c>
       <c r="H38" t="n">
-        <v>2.275</v>
+        <v>2.941</v>
       </c>
       <c r="I38" t="n">
-        <v>2.275</v>
+        <v>3.0168</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.4591</v>
       </c>
       <c r="K38" t="n">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M38" t="n">
-        <v>2.275</v>
+        <v>2.5577</v>
       </c>
       <c r="N38" t="n">
-        <v>270</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.121</v>
+        <v>2.2135</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7389</v>
+        <v>0.7711</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3413</v>
+        <v>0.3749</v>
       </c>
       <c r="E39" t="n">
-        <v>2.121</v>
+        <v>2.2135</v>
       </c>
       <c r="F39" t="n">
-        <v>2.5801</v>
+        <v>2.3322</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.4591</v>
+        <v>-0.0069</v>
       </c>
       <c r="H39" t="n">
-        <v>2.922</v>
+        <v>2.3795</v>
       </c>
       <c r="I39" t="n">
-        <v>2.9973</v>
+        <v>2.3795</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.4591</v>
+        <v>-0.0069</v>
       </c>
       <c r="K39" t="n">
-        <v>261</v>
+        <v>178</v>
       </c>
       <c r="L39" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M39" t="n">
-        <v>2.5382</v>
+        <v>2.3726</v>
       </c>
       <c r="N39" t="n">
-        <v>309</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.9909</v>
+        <v>2.0496</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6936</v>
+        <v>0.714</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2821</v>
+        <v>0.3017</v>
       </c>
       <c r="E40" t="n">
-        <v>1.9909</v>
+        <v>2.0496</v>
       </c>
       <c r="F40" t="n">
-        <v>1.9909</v>
+        <v>1.9995</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.9909</v>
+        <v>1.9995</v>
       </c>
       <c r="I40" t="n">
-        <v>1.9909</v>
+        <v>1.9995</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.9909</v>
+        <v>1.9995</v>
       </c>
       <c r="N40" t="n">
         <v>273</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.9497</v>
+        <v>2.004</v>
       </c>
       <c r="C41" t="n">
-        <v>0.6792</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2633</v>
+        <v>0.2813</v>
       </c>
       <c r="E41" t="n">
-        <v>1.9497</v>
+        <v>2.004</v>
       </c>
       <c r="F41" t="n">
-        <v>2.0003</v>
+        <v>2.0008</v>
       </c>
       <c r="G41" t="n">
         <v>-0.0506</v>
       </c>
       <c r="H41" t="n">
-        <v>2.0003</v>
+        <v>2.0008</v>
       </c>
       <c r="I41" t="n">
-        <v>2.0003</v>
+        <v>2.0008</v>
       </c>
       <c r="J41" t="n">
         <v>-0.0506</v>
@@ -2323,7 +2323,7 @@
         <v>49</v>
       </c>
       <c r="M41" t="n">
-        <v>1.9497</v>
+        <v>1.9502</v>
       </c>
       <c r="N41" t="n">
         <v>227</v>
@@ -2332,139 +2332,139 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.9239</v>
+        <v>1.9512</v>
       </c>
       <c r="C42" t="n">
-        <v>0.6702</v>
+        <v>0.6797</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2516</v>
+        <v>0.2577</v>
       </c>
       <c r="E42" t="n">
-        <v>1.9239</v>
+        <v>1.9512</v>
       </c>
       <c r="F42" t="n">
-        <v>1.9239</v>
+        <v>1.8839</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.9239</v>
+        <v>1.8839</v>
       </c>
       <c r="I42" t="n">
-        <v>1.9239</v>
+        <v>1.8839</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>273</v>
+        <v>220</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.9239</v>
+        <v>1.8839</v>
       </c>
       <c r="N42" t="n">
-        <v>273</v>
+        <v>220</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kyuubii</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.8883</v>
+        <v>1.8225</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.6349</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2354</v>
+        <v>0.2003</v>
       </c>
       <c r="E43" t="n">
-        <v>1.8883</v>
+        <v>1.8225</v>
       </c>
       <c r="F43" t="n">
-        <v>1.8883</v>
+        <v>1.8891</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.8883</v>
+        <v>1.8891</v>
       </c>
       <c r="I43" t="n">
-        <v>1.8883</v>
+        <v>1.8891</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>238</v>
+        <v>273</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.8883</v>
+        <v>1.8891</v>
       </c>
       <c r="N43" t="n">
-        <v>238</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.8439</v>
+        <v>1.796</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6424</v>
+        <v>0.6257</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2152</v>
+        <v>0.1884</v>
       </c>
       <c r="E44" t="n">
-        <v>1.8439</v>
+        <v>1.796</v>
       </c>
       <c r="F44" t="n">
-        <v>1.8439</v>
+        <v>1.7291</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.8439</v>
+        <v>1.7291</v>
       </c>
       <c r="I44" t="n">
-        <v>1.8439</v>
+        <v>1.7291</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>220</v>
+        <v>168</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.8439</v>
+        <v>1.7291</v>
       </c>
       <c r="N44" t="n">
-        <v>220</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45">
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.8113</v>
+        <v>1.7657</v>
       </c>
       <c r="C45" t="n">
-        <v>0.631</v>
+        <v>0.6151</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2003</v>
+        <v>0.1749</v>
       </c>
       <c r="E45" t="n">
-        <v>1.8113</v>
+        <v>1.7657</v>
       </c>
       <c r="F45" t="n">
-        <v>1.8113</v>
+        <v>1.8125</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.8113</v>
+        <v>1.8125</v>
       </c>
       <c r="I45" t="n">
-        <v>1.8113</v>
+        <v>1.8125</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.8113</v>
+        <v>1.8125</v>
       </c>
       <c r="N45" t="n">
         <v>215</v>
@@ -2516,139 +2516,139 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>kyuubii</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.728</v>
+        <v>1.7377</v>
       </c>
       <c r="C46" t="n">
-        <v>0.602</v>
+        <v>0.6054</v>
       </c>
       <c r="D46" t="n">
         <v>0.1624</v>
       </c>
       <c r="E46" t="n">
-        <v>1.728</v>
+        <v>1.7377</v>
       </c>
       <c r="F46" t="n">
-        <v>1.728</v>
+        <v>1.8886</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.728</v>
+        <v>1.8886</v>
       </c>
       <c r="I46" t="n">
-        <v>1.728</v>
+        <v>1.8886</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>168</v>
+        <v>238</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.728</v>
+        <v>1.8886</v>
       </c>
       <c r="N46" t="n">
-        <v>168</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.5504</v>
+        <v>1.592</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5401</v>
+        <v>0.5546</v>
       </c>
       <c r="D47" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0973</v>
       </c>
       <c r="E47" t="n">
-        <v>1.5504</v>
+        <v>1.592</v>
       </c>
       <c r="F47" t="n">
-        <v>1.5504</v>
+        <v>0.159</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1.3093</v>
       </c>
       <c r="H47" t="n">
-        <v>1.5504</v>
+        <v>0.159</v>
       </c>
       <c r="I47" t="n">
-        <v>1.5504</v>
+        <v>0.1631</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1.3093</v>
       </c>
       <c r="K47" t="n">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M47" t="n">
-        <v>1.5504</v>
+        <v>1.4724</v>
       </c>
       <c r="N47" t="n">
-        <v>238</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.469</v>
+        <v>1.4761</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5118</v>
+        <v>0.5142</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0445</v>
+        <v>0.0455</v>
       </c>
       <c r="E48" t="n">
-        <v>1.469</v>
+        <v>1.4761</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1597</v>
+        <v>1.2122</v>
       </c>
       <c r="G48" t="n">
-        <v>1.3093</v>
+        <v>0.1627</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1597</v>
+        <v>1.2122</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1638</v>
+        <v>1.2122</v>
       </c>
       <c r="J48" t="n">
-        <v>1.3093</v>
+        <v>0.1627</v>
       </c>
       <c r="K48" t="n">
-        <v>261</v>
+        <v>178</v>
       </c>
       <c r="L48" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M48" t="n">
-        <v>1.4731</v>
+        <v>1.3749</v>
       </c>
       <c r="N48" t="n">
-        <v>309</v>
+        <v>227</v>
       </c>
     </row>
     <row r="49">
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.3847</v>
+        <v>1.4076</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4824</v>
+        <v>0.4904</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0061</v>
+        <v>0.0149</v>
       </c>
       <c r="E49" t="n">
-        <v>1.3847</v>
+        <v>1.4076</v>
       </c>
       <c r="F49" t="n">
         <v>1.3847</v>
@@ -2700,47 +2700,47 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.3746</v>
+        <v>1.2568</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4789</v>
+        <v>0.4378</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0015</v>
+        <v>-0.0524</v>
       </c>
       <c r="E50" t="n">
-        <v>1.3746</v>
+        <v>1.2568</v>
       </c>
       <c r="F50" t="n">
-        <v>1.2119</v>
+        <v>1.5187</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1627</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1.2119</v>
+        <v>1.5187</v>
       </c>
       <c r="I50" t="n">
-        <v>1.2119</v>
+        <v>1.5187</v>
       </c>
       <c r="J50" t="n">
-        <v>0.1627</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="L50" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.3746</v>
+        <v>1.5187</v>
       </c>
       <c r="N50" t="n">
-        <v>227</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.2245</v>
+        <v>1.1167</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4266</v>
+        <v>0.389</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.0668</v>
+        <v>-0.115</v>
       </c>
       <c r="E51" t="n">
-        <v>1.2245</v>
+        <v>1.1167</v>
       </c>
       <c r="F51" t="n">
-        <v>1.2245</v>
+        <v>1.213</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1.2245</v>
+        <v>1.213</v>
       </c>
       <c r="I51" t="n">
-        <v>1.2245</v>
+        <v>1.213</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1.2245</v>
+        <v>1.213</v>
       </c>
       <c r="N51" t="n">
         <v>168</v>
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.1572</v>
+        <v>0.9328</v>
       </c>
       <c r="C52" t="n">
-        <v>0.4031</v>
+        <v>0.325</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.0974</v>
+        <v>-0.1972</v>
       </c>
       <c r="E52" t="n">
-        <v>1.1572</v>
+        <v>0.9328</v>
       </c>
       <c r="F52" t="n">
-        <v>1.1572</v>
+        <v>1.1447</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.1572</v>
+        <v>1.1447</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1572</v>
+        <v>1.1447</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>1.1572</v>
+        <v>1.1447</v>
       </c>
       <c r="N52" t="n">
         <v>270</v>
@@ -2838,277 +2838,277 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.0034</v>
+        <v>0.8079</v>
       </c>
       <c r="C53" t="n">
-        <v>0.3496</v>
+        <v>0.2814</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.1674</v>
+        <v>-0.2529</v>
       </c>
       <c r="E53" t="n">
-        <v>1.0034</v>
+        <v>0.8079</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6712</v>
+        <v>0.8451</v>
       </c>
       <c r="G53" t="n">
-        <v>0.3322</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6712</v>
+        <v>0.8451</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6885</v>
+        <v>0.8451</v>
       </c>
       <c r="J53" t="n">
-        <v>0.3322</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>264</v>
+        <v>168</v>
       </c>
       <c r="L53" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>1.0207</v>
+        <v>0.8451</v>
       </c>
       <c r="N53" t="n">
-        <v>463</v>
+        <v>168</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8447</v>
+        <v>0.7748</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2943</v>
+        <v>0.2699</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.2397</v>
+        <v>-0.2677</v>
       </c>
       <c r="E54" t="n">
-        <v>0.8447</v>
+        <v>0.7748</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8447</v>
+        <v>0.6454</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>0.3304</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8447</v>
+        <v>0.6454</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8447</v>
+        <v>0.662</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>0.3304</v>
       </c>
       <c r="K54" t="n">
-        <v>168</v>
+        <v>264</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="M54" t="n">
-        <v>0.8447</v>
+        <v>0.9924000000000001</v>
       </c>
       <c r="N54" t="n">
-        <v>168</v>
+        <v>463</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>susp</t>
+          <t>twenty3</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7124</v>
+        <v>0.6715</v>
       </c>
       <c r="C55" t="n">
-        <v>0.2482</v>
+        <v>0.2339</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.2999</v>
+        <v>-0.3139</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7124</v>
+        <v>0.6715</v>
       </c>
       <c r="F55" t="n">
-        <v>0.7124</v>
+        <v>0.4543</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.7124</v>
+        <v>0.4543</v>
       </c>
       <c r="I55" t="n">
-        <v>0.7124</v>
+        <v>0.4543</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>215</v>
+        <v>101</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7124</v>
+        <v>0.4543</v>
       </c>
       <c r="N55" t="n">
-        <v>215</v>
+        <v>101</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>roman</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.704</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2453</v>
+        <v>0.2021</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.3037</v>
+        <v>-0.3547</v>
       </c>
       <c r="E56" t="n">
-        <v>0.704</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7119</v>
+        <v>0.178</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.4771</v>
       </c>
       <c r="H56" t="n">
-        <v>0.7119</v>
+        <v>0.178</v>
       </c>
       <c r="I56" t="n">
-        <v>0.7119</v>
+        <v>0.178</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.4771</v>
       </c>
       <c r="K56" t="n">
-        <v>178</v>
+        <v>252</v>
       </c>
       <c r="L56" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="M56" t="n">
-        <v>0.704</v>
+        <v>0.6551</v>
       </c>
       <c r="N56" t="n">
-        <v>227</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>roman</t>
+          <t>susp</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.5049</v>
       </c>
       <c r="C57" t="n">
-        <v>0.2281</v>
+        <v>0.1759</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.3262</v>
+        <v>-0.3883</v>
       </c>
       <c r="E57" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.5049</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1771</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>0.4776</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1771</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1771</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>0.4776</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="L57" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.6547000000000001</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="N57" t="n">
-        <v>291</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>twenty3</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4168</v>
+        <v>0.4649</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1452</v>
+        <v>0.162</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4345</v>
+        <v>-0.4062</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4168</v>
+        <v>0.4649</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4168</v>
+        <v>0.7123</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4168</v>
+        <v>0.7123</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4168</v>
+        <v>0.7123</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M58" t="n">
-        <v>0.4168</v>
+        <v>0.7044</v>
       </c>
       <c r="N58" t="n">
-        <v>101</v>
+        <v>227</v>
       </c>
     </row>
     <row r="59">
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.1354</v>
+        <v>0.0682</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0472</v>
+        <v>0.0238</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5626</v>
+        <v>-0.5834</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1354</v>
+        <v>0.0682</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1354</v>
+        <v>0.1654</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1354</v>
+        <v>0.1654</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1354</v>
+        <v>0.1654</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1354</v>
+        <v>0.1654</v>
       </c>
       <c r="N59" t="n">
         <v>220</v>
@@ -3160,308 +3160,308 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ag1l</t>
+          <t>Cxzi</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0511</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0178</v>
+        <v>-0.0273</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6009</v>
+        <v>-0.6488</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0511</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.1257</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>0.1768</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.1257</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1257</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>0.1768</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>252</v>
+        <v>168</v>
       </c>
       <c r="L60" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.05110000000000001</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="N60" t="n">
-        <v>291</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cxzi</t>
+          <t>Ag1l</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0106</v>
+        <v>-0.1459</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0037</v>
+        <v>-0.0508</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6194</v>
+        <v>-0.679</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0106</v>
+        <v>-0.1459</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0106</v>
+        <v>-0.138</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>0.1766</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0106</v>
+        <v>-0.138</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0106</v>
+        <v>-0.138</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>0.1766</v>
       </c>
       <c r="K61" t="n">
-        <v>168</v>
+        <v>252</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M61" t="n">
-        <v>0.0106</v>
+        <v>0.0386</v>
       </c>
       <c r="N61" t="n">
-        <v>168</v>
+        <v>291</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.1171</v>
+        <v>-0.3791</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.0408</v>
+        <v>-0.1321</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6775</v>
+        <v>-0.7832</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.1171</v>
+        <v>-0.3791</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.1171</v>
+        <v>-0.319</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.1171</v>
+        <v>-0.319</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.1171</v>
+        <v>-0.319</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>220</v>
+        <v>164</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.1171</v>
+        <v>-0.319</v>
       </c>
       <c r="N62" t="n">
-        <v>220</v>
+        <v>164</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.1341</v>
+        <v>-0.4092</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.0467</v>
+        <v>-0.1426</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6852</v>
+        <v>-0.7966</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.1341</v>
+        <v>-0.4092</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.1341</v>
+        <v>-0.1416</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.1341</v>
+        <v>-0.1416</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1341</v>
+        <v>-0.1416</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>164</v>
+        <v>215</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.1341</v>
+        <v>-0.1416</v>
       </c>
       <c r="N63" t="n">
-        <v>164</v>
+        <v>215</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.1551</v>
+        <v>-0.4145</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.054</v>
+        <v>-0.1444</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6948</v>
+        <v>-0.799</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.1551</v>
+        <v>-0.4145</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.1551</v>
+        <v>0.0336</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>-0.3159</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.1551</v>
+        <v>0.0336</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1551</v>
+        <v>0.0345</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>-0.3159</v>
       </c>
       <c r="K64" t="n">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.1551</v>
+        <v>-0.2814</v>
       </c>
       <c r="N64" t="n">
-        <v>215</v>
+        <v>309</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.2816</v>
+        <v>-0.4242</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.1478</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7524</v>
+        <v>-0.8033</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.2816</v>
+        <v>-0.4242</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0343</v>
+        <v>-0.1294</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.3159</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0343</v>
+        <v>-0.1294</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0352</v>
+        <v>-0.1294</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.3159</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="L65" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.2807</v>
+        <v>-0.1294</v>
       </c>
       <c r="N65" t="n">
-        <v>309</v>
+        <v>220</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.319</v>
+        <v>-0.487</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1111</v>
+        <v>-0.1697</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7694</v>
+        <v>-0.8314</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.319</v>
+        <v>-0.487</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.319</v>
+        <v>-0.1341</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.319</v>
+        <v>-0.1341</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.319</v>
+        <v>-0.1341</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.319</v>
+        <v>-0.1341</v>
       </c>
       <c r="N66" t="n">
         <v>164</v>
@@ -3486,28 +3486,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.656</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1814</v>
+        <v>-0.2285</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8612</v>
+        <v>-0.9068000000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.656</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.522</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.522</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.522</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.522</v>
       </c>
       <c r="N67" t="n">
         <v>273</v>
@@ -3528,47 +3528,47 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>JBa</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.802</v>
+        <v>-0.8306</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2794</v>
+        <v>-0.2894</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9893</v>
+        <v>-0.9848</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.802</v>
+        <v>-0.8306</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.802</v>
+        <v>-0.9147</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.802</v>
+        <v>-0.9147</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.802</v>
+        <v>-0.9147</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.802</v>
+        <v>-0.9147</v>
       </c>
       <c r="N68" t="n">
-        <v>215</v>
+        <v>164</v>
       </c>
     </row>
     <row r="69">
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.9143</v>
+        <v>-0.9952</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3185</v>
+        <v>-0.3467</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0404</v>
+        <v>-1.0584</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.9143</v>
+        <v>-0.9952</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.9143</v>
+        <v>-0.9022</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.9143</v>
+        <v>-0.9022</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.9143</v>
+        <v>-0.9022</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.9143</v>
+        <v>-0.9022</v>
       </c>
       <c r="N69" t="n">
         <v>273</v>
@@ -3620,47 +3620,47 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>JBa</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.9147</v>
+        <v>-1.076</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3187</v>
+        <v>-0.3748</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0406</v>
+        <v>-1.0944</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.9147</v>
+        <v>-1.076</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.9147</v>
+        <v>-0.8401</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.9147</v>
+        <v>-0.8401</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.9147</v>
+        <v>-0.8401</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>164</v>
+        <v>215</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.9147</v>
+        <v>-0.8401</v>
       </c>
       <c r="N70" t="n">
-        <v>164</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71">
@@ -3670,31 +3670,31 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.0829</v>
+        <v>-1.3597</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3772</v>
+        <v>-0.4737</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.1172</v>
+        <v>-1.2212</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.0829</v>
+        <v>-1.3597</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.7879</v>
+        <v>-0.7872</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.295</v>
+        <v>-0.2951</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.7879</v>
+        <v>-0.7872</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7879</v>
+        <v>-0.7872</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.295</v>
+        <v>-0.2951</v>
       </c>
       <c r="K71" t="n">
         <v>252</v>
@@ -3703,7 +3703,7 @@
         <v>39</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.0829</v>
+        <v>-1.0823</v>
       </c>
       <c r="N71" t="n">
         <v>291</v>
@@ -3716,31 +3716,31 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.179</v>
+        <v>-1.4669</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4107</v>
+        <v>-0.511</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1609</v>
+        <v>-1.2691</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.179</v>
+        <v>-1.4669</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.9789</v>
+        <v>-1.0256</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.2001</v>
+        <v>-0.2002</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.9789</v>
+        <v>-1.0256</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.0041</v>
+        <v>-1.052</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.2001</v>
+        <v>-0.2002</v>
       </c>
       <c r="K72" t="n">
         <v>203</v>
@@ -3749,7 +3749,7 @@
         <v>64</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.2042</v>
+        <v>-1.2522</v>
       </c>
       <c r="N72" t="n">
         <v>267</v>
@@ -3758,78 +3758,78 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kauez</t>
+          <t>ANa</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.5937</v>
+        <v>-1.5316</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5552</v>
+        <v>-0.5336</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.3497</v>
+        <v>-1.298</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.5937</v>
+        <v>-1.5316</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.1011</v>
+        <v>-1.6731</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.4926</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.1011</v>
+        <v>-1.6731</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1295</v>
+        <v>-1.6731</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.4926</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>261</v>
+        <v>101</v>
       </c>
       <c r="L73" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.6221</v>
+        <v>-1.6731</v>
       </c>
       <c r="N73" t="n">
-        <v>309</v>
+        <v>101</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ANa</t>
+          <t>tory</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.6717</v>
+        <v>-1.7807</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5824</v>
+        <v>-0.6203</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.3852</v>
+        <v>-1.4092</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.6717</v>
+        <v>-1.7807</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.6717</v>
+        <v>-1.8305</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.6717</v>
+        <v>-1.8305</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.6717</v>
+        <v>-1.8305</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.6717</v>
+        <v>-1.8305</v>
       </c>
       <c r="N74" t="n">
         <v>101</v>
@@ -3850,47 +3850,47 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>tory</t>
+          <t>kauez</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.8494</v>
+        <v>-1.9132</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.6443</v>
+        <v>-0.6665</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.4661</v>
+        <v>-1.4684</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.8494</v>
+        <v>-1.9132</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.8494</v>
+        <v>-1.1024</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>-0.4926</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.8494</v>
+        <v>-1.1024</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.8494</v>
+        <v>-1.1308</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>-0.4926</v>
       </c>
       <c r="K75" t="n">
-        <v>101</v>
+        <v>261</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.8494</v>
+        <v>-1.6234</v>
       </c>
       <c r="N75" t="n">
-        <v>101</v>
+        <v>309</v>
       </c>
     </row>
     <row r="76">
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.8775</v>
+        <v>-2.0345</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.6541</v>
+        <v>-0.7088</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.4789</v>
+        <v>-1.5226</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.8775</v>
+        <v>-2.0345</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.8775</v>
+        <v>-1.8638</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.8775</v>
+        <v>-1.8638</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.8775</v>
+        <v>-1.8638</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.8775</v>
+        <v>-1.8638</v>
       </c>
       <c r="N76" t="n">
         <v>270</v>
@@ -3942,93 +3942,93 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>Kat</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-2.2583</v>
+        <v>-2.4538</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7867</v>
+        <v>-0.8548</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.6522</v>
+        <v>-1.7099</v>
       </c>
       <c r="E77" t="n">
-        <v>-2.2583</v>
+        <v>-2.4538</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.1335</v>
+        <v>-2.3912</v>
       </c>
       <c r="G77" t="n">
-        <v>-1.1248</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.1335</v>
+        <v>-2.3912</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.1627</v>
+        <v>-2.3912</v>
       </c>
       <c r="J77" t="n">
-        <v>-1.1248</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>238</v>
+        <v>101</v>
       </c>
       <c r="L77" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-2.2875</v>
+        <v>-2.3912</v>
       </c>
       <c r="N77" t="n">
-        <v>427</v>
+        <v>101</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kat</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.3822</v>
+        <v>-2.5308</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.8299</v>
+        <v>-0.8817</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.7086</v>
+        <v>-1.7443</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.3822</v>
+        <v>-2.5308</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.3822</v>
+        <v>-1.1334</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>-1.1229</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.3822</v>
+        <v>-1.1334</v>
       </c>
       <c r="I78" t="n">
-        <v>-2.3822</v>
+        <v>-1.1626</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>-1.1229</v>
       </c>
       <c r="K78" t="n">
-        <v>101</v>
+        <v>238</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="M78" t="n">
-        <v>-2.3822</v>
+        <v>-2.2855</v>
       </c>
       <c r="N78" t="n">
-        <v>101</v>
+        <v>427</v>
       </c>
     </row>
     <row r="79">
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.4565</v>
+        <v>-2.935</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.8558</v>
+        <v>-1.0225</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.7425</v>
+        <v>-1.9248</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.4565</v>
+        <v>-2.935</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.4565</v>
+        <v>-2.4568</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.4565</v>
+        <v>-2.4568</v>
       </c>
       <c r="I79" t="n">
-        <v>-2.4565</v>
+        <v>-2.4568</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.4565</v>
+        <v>-2.4568</v>
       </c>
       <c r="N79" t="n">
         <v>101</v>
@@ -4084,22 +4084,22 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.6472</v>
+        <v>-3.9699</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.2706</v>
+        <v>-1.383</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.2845</v>
+        <v>-2.3871</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.6472</v>
+        <v>-3.9699</v>
       </c>
       <c r="F80" t="n">
         <v>-1.904</v>
       </c>
       <c r="G80" t="n">
-        <v>-1.7432</v>
+        <v>-1.7524</v>
       </c>
       <c r="H80" t="n">
         <v>-1.904</v>
@@ -4108,7 +4108,7 @@
         <v>-1.904</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.7432</v>
+        <v>-1.7524</v>
       </c>
       <c r="K80" t="n">
         <v>241</v>
@@ -4117,7 +4117,7 @@
         <v>82</v>
       </c>
       <c r="M80" t="n">
-        <v>-3.6472</v>
+        <v>-3.6564</v>
       </c>
       <c r="N80" t="n">
         <v>323</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4.4171</v>
+        <v>-4.7979</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.5388</v>
+        <v>-1.6714</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.635</v>
+        <v>-2.7569</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.4171</v>
+        <v>-4.7979</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.6389</v>
+        <v>-3.6492</v>
       </c>
       <c r="G81" t="n">
         <v>-0.7782</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.6389</v>
+        <v>-3.6492</v>
       </c>
       <c r="I81" t="n">
-        <v>-3.8288</v>
+        <v>-3.8397</v>
       </c>
       <c r="J81" t="n">
         <v>-0.7782</v>
@@ -4163,7 +4163,7 @@
         <v>118</v>
       </c>
       <c r="M81" t="n">
-        <v>-4.607</v>
+        <v>-4.617900000000001</v>
       </c>
       <c r="N81" t="n">
         <v>512</v>
@@ -4269,10 +4269,10 @@
         <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0786</v>
+        <v>1.077</v>
       </c>
       <c r="J2" t="n">
-        <v>20.4934</v>
+        <v>20.463</v>
       </c>
     </row>
     <row r="3">
@@ -4306,13 +4306,13 @@
         <v>19</v>
       </c>
       <c r="H3" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9268</v>
+        <v>0.9637</v>
       </c>
       <c r="J3" t="n">
-        <v>17.6092</v>
+        <v>18.3103</v>
       </c>
     </row>
     <row r="4">
@@ -4346,13 +4346,13 @@
         <v>19</v>
       </c>
       <c r="H4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6684</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>12.6996</v>
+        <v>13.072</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>1.26</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6684</v>
+        <v>0.6675</v>
       </c>
       <c r="J5" t="n">
-        <v>12.6996</v>
+        <v>12.6825</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.71</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8265</v>
+        <v>-0.8274</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.7035</v>
+        <v>-15.7206</v>
       </c>
     </row>
     <row r="7">
@@ -4869,10 +4869,10 @@
         <v>2.14</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1857</v>
+        <v>1.1861</v>
       </c>
       <c r="J17" t="n">
-        <v>20.1569</v>
+        <v>20.1637</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>2.05</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1077</v>
+        <v>1.1081</v>
       </c>
       <c r="J18" t="n">
-        <v>18.8309</v>
+        <v>18.8377</v>
       </c>
     </row>
     <row r="19">
@@ -4946,13 +4946,13 @@
         <v>17</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1545</v>
+        <v>0.1401</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6265</v>
+        <v>2.3817</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.91</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.164</v>
+        <v>-0.1639</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.788</v>
+        <v>-2.7863</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3826</v>
+        <v>-0.3825</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.5042</v>
+        <v>-6.5025</v>
       </c>
     </row>
     <row r="22">
@@ -6269,10 +6269,10 @@
         <v>1.7</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3664</v>
+        <v>1.3669</v>
       </c>
       <c r="J52" t="n">
-        <v>28.6944</v>
+        <v>28.7049</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>1.68</v>
       </c>
       <c r="I53" t="n">
-        <v>1.3404</v>
+        <v>1.3409</v>
       </c>
       <c r="J53" t="n">
-        <v>28.1484</v>
+        <v>28.1589</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>1.2</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5436</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>11.4156</v>
+        <v>11.4219</v>
       </c>
     </row>
     <row r="55">
@@ -6386,13 +6386,13 @@
         <v>21</v>
       </c>
       <c r="H55" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.718</v>
       </c>
       <c r="J55" t="n">
-        <v>-14.6181</v>
+        <v>-15.078</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.74</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7621</v>
+        <v>-0.7618</v>
       </c>
       <c r="J56" t="n">
-        <v>-16.0041</v>
+        <v>-15.9978</v>
       </c>
     </row>
     <row r="57">
@@ -7066,13 +7066,13 @@
         <v>24</v>
       </c>
       <c r="H72" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0377</v>
+        <v>1.0244</v>
       </c>
       <c r="J72" t="n">
-        <v>24.9048</v>
+        <v>24.5856</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.39</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8236</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>19.7664</v>
+        <v>19.7784</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>1.22</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5619</v>
+        <v>0.5622</v>
       </c>
       <c r="J74" t="n">
-        <v>13.4856</v>
+        <v>13.4928</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>0.77</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.6757</v>
+        <v>-0.6753</v>
       </c>
       <c r="J75" t="n">
-        <v>-16.2168</v>
+        <v>-16.2072</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>0.58</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.0751</v>
+        <v>-1.0748</v>
       </c>
       <c r="J76" t="n">
-        <v>-25.8024</v>
+        <v>-25.7952</v>
       </c>
     </row>
     <row r="77">
@@ -7466,13 +7466,13 @@
         <v>19</v>
       </c>
       <c r="H82" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I82" t="n">
-        <v>1.258</v>
+        <v>1.2738</v>
       </c>
       <c r="J82" t="n">
-        <v>23.902</v>
+        <v>24.2022</v>
       </c>
     </row>
     <row r="83">
@@ -7506,13 +7506,13 @@
         <v>19</v>
       </c>
       <c r="H83" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9303</v>
+        <v>0.8914</v>
       </c>
       <c r="J83" t="n">
-        <v>17.6757</v>
+        <v>16.9366</v>
       </c>
     </row>
     <row r="84">
@@ -7546,13 +7546,13 @@
         <v>19</v>
       </c>
       <c r="H84" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5747</v>
+        <v>0.5603</v>
       </c>
       <c r="J84" t="n">
-        <v>10.9193</v>
+        <v>10.6457</v>
       </c>
     </row>
     <row r="85">
@@ -7586,13 +7586,13 @@
         <v>19</v>
       </c>
       <c r="H85" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="I85" t="n">
-        <v>0.5117</v>
+        <v>0.4966</v>
       </c>
       <c r="J85" t="n">
-        <v>9.722300000000001</v>
+        <v>9.4354</v>
       </c>
     </row>
     <row r="86">
@@ -7626,13 +7626,13 @@
         <v>19</v>
       </c>
       <c r="H86" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.9378</v>
+        <v>-0.977</v>
       </c>
       <c r="J86" t="n">
-        <v>-17.8182</v>
+        <v>-18.563</v>
       </c>
     </row>
     <row r="87">
@@ -7669,16 +7669,16 @@
         <v>1.07</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2251</v>
+        <v>0.2245</v>
       </c>
       <c r="J87" t="n">
-        <v>4.2769</v>
+        <v>4.2655</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7709,16 +7709,16 @@
         <v>0.96</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0602</v>
+        <v>-0.0604</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.1438</v>
+        <v>-1.1476</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7746,13 +7746,13 @@
         <v>19</v>
       </c>
       <c r="H89" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0604</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.6606</v>
+        <v>-1.1476</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>0.67</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3609</v>
+        <v>-0.3611</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.8571</v>
+        <v>-6.8609</v>
       </c>
     </row>
     <row r="91">
@@ -7826,13 +7826,13 @@
         <v>19</v>
       </c>
       <c r="H91" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.397</v>
+        <v>-0.4062</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.543</v>
+        <v>-7.7178</v>
       </c>
     </row>
     <row r="92">
@@ -7866,13 +7866,13 @@
         <v>30</v>
       </c>
       <c r="H92" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I92" t="n">
-        <v>1.0238</v>
+        <v>1.037</v>
       </c>
       <c r="J92" t="n">
-        <v>30.714</v>
+        <v>31.11</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>1.16</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4553</v>
+        <v>0.4551</v>
       </c>
       <c r="J93" t="n">
-        <v>13.659</v>
+        <v>13.653</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>1.11</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3436</v>
+        <v>0.3433</v>
       </c>
       <c r="J94" t="n">
-        <v>10.308</v>
+        <v>10.299</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.0247</v>
+        <v>-0.025</v>
       </c>
       <c r="J95" t="n">
-        <v>-0.741</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2588</v>
+        <v>-0.2591</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.764</v>
+        <v>-7.773</v>
       </c>
     </row>
     <row r="97">
@@ -9066,13 +9066,13 @@
         <v>17</v>
       </c>
       <c r="H122" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2427</v>
+        <v>1.2306</v>
       </c>
       <c r="J122" t="n">
-        <v>21.1259</v>
+        <v>20.9202</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>1.62</v>
       </c>
       <c r="I123" t="n">
-        <v>1.0903</v>
+        <v>1.0907</v>
       </c>
       <c r="J123" t="n">
-        <v>18.5351</v>
+        <v>18.5419</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>1.36</v>
       </c>
       <c r="I124" t="n">
-        <v>0.7425</v>
+        <v>0.7427</v>
       </c>
       <c r="J124" t="n">
-        <v>12.6225</v>
+        <v>12.6259</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>1.07</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2069</v>
+        <v>0.2072</v>
       </c>
       <c r="J125" t="n">
-        <v>3.5173</v>
+        <v>3.5224</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.87</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.479</v>
+        <v>-0.4787</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.143000000000001</v>
+        <v>-8.1379</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.36</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6362</v>
+        <v>0.6357</v>
       </c>
       <c r="J127" t="n">
-        <v>10.8154</v>
+        <v>10.8069</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.07</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1999</v>
+        <v>0.1995</v>
       </c>
       <c r="J128" t="n">
-        <v>3.3983</v>
+        <v>3.3915</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>0.99</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0226</v>
+        <v>-0.0227</v>
       </c>
       <c r="J129" t="n">
-        <v>-0.3842</v>
+        <v>-0.3859</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2382</v>
+        <v>-0.2384</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.0494</v>
+        <v>-4.0528</v>
       </c>
     </row>
     <row r="131">
@@ -9426,13 +9426,13 @@
         <v>17</v>
       </c>
       <c r="H131" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4854</v>
+        <v>-0.477</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.251799999999999</v>
+        <v>-8.109</v>
       </c>
     </row>
     <row r="132">
@@ -10266,13 +10266,13 @@
         <v>19</v>
       </c>
       <c r="H152" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="I152" t="n">
-        <v>0.2768</v>
+        <v>0.2624</v>
       </c>
       <c r="J152" t="n">
-        <v>5.2592</v>
+        <v>4.9856</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>0.98</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0349</v>
+        <v>-0.0347</v>
       </c>
       <c r="J153" t="n">
-        <v>-0.6631</v>
+        <v>-0.6593</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>0.86</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1819</v>
+        <v>-0.1817</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.4561</v>
+        <v>-3.4523</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>0.77</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.272</v>
+        <v>-0.2718</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.168</v>
+        <v>-5.1642</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.74</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3007</v>
+        <v>-0.3004</v>
       </c>
       <c r="J156" t="n">
-        <v>-5.7133</v>
+        <v>-5.7076</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>1.56</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6112</v>
+        <v>0.611</v>
       </c>
       <c r="J157" t="n">
-        <v>11.6128</v>
+        <v>11.609</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>1.43</v>
       </c>
       <c r="I158" t="n">
-        <v>0.515</v>
+        <v>0.5148</v>
       </c>
       <c r="J158" t="n">
-        <v>9.785</v>
+        <v>9.7812</v>
       </c>
     </row>
     <row r="159">
@@ -10546,13 +10546,13 @@
         <v>19</v>
       </c>
       <c r="H159" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3738</v>
+        <v>0.3845</v>
       </c>
       <c r="J159" t="n">
-        <v>7.1022</v>
+        <v>7.3055</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>1.23</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3286</v>
+        <v>0.3285</v>
       </c>
       <c r="J160" t="n">
-        <v>6.2434</v>
+        <v>6.2415</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>0.95</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.1084</v>
+        <v>-0.1085</v>
       </c>
       <c r="J161" t="n">
-        <v>-2.0596</v>
+        <v>-2.0615</v>
       </c>
     </row>
     <row r="162">
@@ -12669,10 +12669,10 @@
         <v>1.39</v>
       </c>
       <c r="I212" t="n">
-        <v>0.915</v>
+        <v>0.9153</v>
       </c>
       <c r="J212" t="n">
-        <v>19.215</v>
+        <v>19.2213</v>
       </c>
     </row>
     <row r="213">
@@ -12706,13 +12706,13 @@
         <v>21</v>
       </c>
       <c r="H213" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8193</v>
+        <v>0.8002</v>
       </c>
       <c r="J213" t="n">
-        <v>17.2053</v>
+        <v>16.8042</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>1.33</v>
       </c>
       <c r="I214" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.8002</v>
       </c>
       <c r="J214" t="n">
-        <v>16.7979</v>
+        <v>16.8042</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>1.29</v>
       </c>
       <c r="I215" t="n">
-        <v>0.7217</v>
+        <v>0.7219</v>
       </c>
       <c r="J215" t="n">
-        <v>15.1557</v>
+        <v>15.1599</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>1.02</v>
       </c>
       <c r="I216" t="n">
-        <v>0.055</v>
+        <v>0.0553</v>
       </c>
       <c r="J216" t="n">
-        <v>1.155</v>
+        <v>1.1613</v>
       </c>
     </row>
     <row r="217">
@@ -13669,10 +13669,10 @@
         <v>0.93</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.0633</v>
+        <v>-0.065</v>
       </c>
       <c r="J237" t="n">
-        <v>-0.9495</v>
+        <v>-0.975</v>
       </c>
     </row>
     <row r="238">
@@ -13706,13 +13706,13 @@
         <v>15</v>
       </c>
       <c r="H238" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.1143</v>
+        <v>-0.1036</v>
       </c>
       <c r="J238" t="n">
-        <v>-1.7145</v>
+        <v>-1.554</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>0.57</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4276</v>
+        <v>-0.4284</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.414</v>
+        <v>-6.426</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4364</v>
+        <v>-0.4373</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.546</v>
+        <v>-6.5595</v>
       </c>
     </row>
     <row r="241">
@@ -13826,13 +13826,13 @@
         <v>15</v>
       </c>
       <c r="H241" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6029</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.0435</v>
+        <v>-8.792999999999999</v>
       </c>
     </row>
     <row r="242">
@@ -13866,13 +13866,13 @@
         <v>23</v>
       </c>
       <c r="H242" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I242" t="n">
-        <v>0.7773</v>
+        <v>0.7902</v>
       </c>
       <c r="J242" t="n">
-        <v>17.8779</v>
+        <v>18.1746</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>1.01</v>
       </c>
       <c r="I243" t="n">
-        <v>0.0472</v>
+        <v>0.0464</v>
       </c>
       <c r="J243" t="n">
-        <v>1.0856</v>
+        <v>1.0672</v>
       </c>
     </row>
     <row r="244">
@@ -13946,13 +13946,13 @@
         <v>23</v>
       </c>
       <c r="H244" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.0704</v>
+        <v>-0.0567</v>
       </c>
       <c r="J244" t="n">
-        <v>-1.6192</v>
+        <v>-1.3041</v>
       </c>
     </row>
     <row r="245">
@@ -13986,13 +13986,13 @@
         <v>23</v>
       </c>
       <c r="H245" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2395</v>
+        <v>-0.23</v>
       </c>
       <c r="J245" t="n">
-        <v>-5.5085</v>
+        <v>-5.29</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>0.65</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3902</v>
+        <v>-0.3907</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.974600000000001</v>
+        <v>-8.9861</v>
       </c>
     </row>
     <row r="247">
@@ -14066,13 +14066,13 @@
         <v>23</v>
       </c>
       <c r="H247" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="I247" t="n">
-        <v>1.3209</v>
+        <v>1.3083</v>
       </c>
       <c r="J247" t="n">
-        <v>30.3807</v>
+        <v>30.0909</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.31</v>
       </c>
       <c r="I248" t="n">
-        <v>0.7653</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="J248" t="n">
-        <v>17.6019</v>
+        <v>17.6088</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>1.15</v>
       </c>
       <c r="I249" t="n">
-        <v>0.427</v>
+        <v>0.4273</v>
       </c>
       <c r="J249" t="n">
-        <v>9.821</v>
+        <v>9.8279</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>1.13</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3789</v>
+        <v>0.3792</v>
       </c>
       <c r="J250" t="n">
-        <v>8.714700000000001</v>
+        <v>8.7216</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.96</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.213</v>
+        <v>-0.2126</v>
       </c>
       <c r="J251" t="n">
-        <v>-4.899</v>
+        <v>-4.8898</v>
       </c>
     </row>
     <row r="252">
@@ -15069,10 +15069,10 @@
         <v>1.58</v>
       </c>
       <c r="I272" t="n">
-        <v>1.223</v>
+        <v>1.2235</v>
       </c>
       <c r="J272" t="n">
-        <v>25.683</v>
+        <v>25.6935</v>
       </c>
     </row>
     <row r="273">
@@ -15106,13 +15106,13 @@
         <v>21</v>
       </c>
       <c r="H273" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="I273" t="n">
-        <v>1.223</v>
+        <v>1.21</v>
       </c>
       <c r="J273" t="n">
-        <v>25.683</v>
+        <v>25.41</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>1.24</v>
       </c>
       <c r="I274" t="n">
-        <v>0.6362</v>
+        <v>0.6365</v>
       </c>
       <c r="J274" t="n">
-        <v>13.3602</v>
+        <v>13.3665</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>0.78</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.664</v>
+        <v>-0.6637</v>
       </c>
       <c r="J275" t="n">
-        <v>-13.944</v>
+        <v>-13.9377</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.62</v>
       </c>
       <c r="I276" t="n">
-        <v>-1.004</v>
+        <v>-1.0037</v>
       </c>
       <c r="J276" t="n">
-        <v>-21.084</v>
+        <v>-21.0777</v>
       </c>
     </row>
     <row r="277">
@@ -16069,10 +16069,10 @@
         <v>1.82</v>
       </c>
       <c r="I297" t="n">
-        <v>1.5117</v>
+        <v>1.5123</v>
       </c>
       <c r="J297" t="n">
-        <v>25.6989</v>
+        <v>25.7091</v>
       </c>
     </row>
     <row r="298">
@@ -16106,13 +16106,13 @@
         <v>17</v>
       </c>
       <c r="H298" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="I298" t="n">
-        <v>0.7451</v>
+        <v>0.7254</v>
       </c>
       <c r="J298" t="n">
-        <v>12.6667</v>
+        <v>12.3318</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>1.14</v>
       </c>
       <c r="I299" t="n">
-        <v>0.4029</v>
+        <v>0.4032</v>
       </c>
       <c r="J299" t="n">
-        <v>6.8493</v>
+        <v>6.8544</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>1.03</v>
       </c>
       <c r="I300" t="n">
-        <v>0.0963</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="J300" t="n">
-        <v>1.6371</v>
+        <v>1.6422</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.2757</v>
+        <v>-0.2754</v>
       </c>
       <c r="J301" t="n">
-        <v>-4.6869</v>
+        <v>-4.6818</v>
       </c>
     </row>
     <row r="302">
@@ -17269,10 +17269,10 @@
         <v>1.37</v>
       </c>
       <c r="I327" t="n">
-        <v>0.6986</v>
+        <v>0.698</v>
       </c>
       <c r="J327" t="n">
-        <v>32.8342</v>
+        <v>32.806</v>
       </c>
     </row>
     <row r="328">
@@ -17306,13 +17306,13 @@
         <v>47</v>
       </c>
       <c r="H328" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="I328" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.5903</v>
       </c>
       <c r="J328" t="n">
-        <v>27.0297</v>
+        <v>27.7441</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>0.92</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.1256</v>
+        <v>-0.1258</v>
       </c>
       <c r="J329" t="n">
-        <v>-5.9032</v>
+        <v>-5.9126</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>0.84</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2141</v>
+        <v>-0.2142</v>
       </c>
       <c r="J330" t="n">
-        <v>-10.0627</v>
+        <v>-10.0674</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>0.7</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3498</v>
+        <v>-0.3499</v>
       </c>
       <c r="J331" t="n">
-        <v>-16.4406</v>
+        <v>-16.4453</v>
       </c>
     </row>
     <row r="332">
@@ -18269,16 +18269,16 @@
         <v>1.49</v>
       </c>
       <c r="I352" t="n">
-        <v>0.8797</v>
+        <v>0.879</v>
       </c>
       <c r="J352" t="n">
-        <v>20.2331</v>
+        <v>20.217</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -18309,16 +18309,16 @@
         <v>1.29</v>
       </c>
       <c r="I353" t="n">
-        <v>0.5783</v>
+        <v>0.5777</v>
       </c>
       <c r="J353" t="n">
-        <v>13.3009</v>
+        <v>13.2871</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -18346,13 +18346,13 @@
         <v>23</v>
       </c>
       <c r="H354" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="I354" t="n">
-        <v>0.5624</v>
+        <v>0.5777</v>
       </c>
       <c r="J354" t="n">
-        <v>12.9352</v>
+        <v>13.2871</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>0.5</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.5238</v>
+        <v>-0.5239</v>
       </c>
       <c r="J355" t="n">
-        <v>-12.0474</v>
+        <v>-12.0497</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.5</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.5238</v>
+        <v>-0.5239</v>
       </c>
       <c r="J356" t="n">
-        <v>-12.0474</v>
+        <v>-12.0497</v>
       </c>
     </row>
     <row r="357">
@@ -19269,10 +19269,10 @@
         <v>1.31</v>
       </c>
       <c r="I377" t="n">
-        <v>0.8042</v>
+        <v>0.8048</v>
       </c>
       <c r="J377" t="n">
-        <v>19.3008</v>
+        <v>19.3152</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>1.15</v>
       </c>
       <c r="I378" t="n">
-        <v>0.4505</v>
+        <v>0.4509</v>
       </c>
       <c r="J378" t="n">
-        <v>10.812</v>
+        <v>10.8216</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>1.1</v>
       </c>
       <c r="I379" t="n">
-        <v>0.327</v>
+        <v>0.3273</v>
       </c>
       <c r="J379" t="n">
-        <v>7.848</v>
+        <v>7.8552</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>0.93</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.2741</v>
+        <v>-0.2737</v>
       </c>
       <c r="J380" t="n">
-        <v>-6.5784</v>
+        <v>-6.5688</v>
       </c>
     </row>
     <row r="381">
@@ -19426,13 +19426,13 @@
         <v>24</v>
       </c>
       <c r="H381" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3834</v>
+        <v>-0.4089</v>
       </c>
       <c r="J381" t="n">
-        <v>-9.201599999999999</v>
+        <v>-9.813599999999999</v>
       </c>
     </row>
     <row r="382">
@@ -19666,13 +19666,13 @@
         <v>21</v>
       </c>
       <c r="H387" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="I387" t="n">
-        <v>0.9406</v>
+        <v>0.9502</v>
       </c>
       <c r="J387" t="n">
-        <v>19.7526</v>
+        <v>19.9542</v>
       </c>
     </row>
     <row r="388">
@@ -19709,10 +19709,10 @@
         <v>0.96</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.0699</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J388" t="n">
-        <v>-1.4679</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="389">
@@ -19749,10 +19749,10 @@
         <v>0.77</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.2775</v>
+        <v>-0.2777</v>
       </c>
       <c r="J389" t="n">
-        <v>-5.8275</v>
+        <v>-5.8317</v>
       </c>
     </row>
     <row r="390">
@@ -19789,10 +19789,10 @@
         <v>0.76</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.2871</v>
+        <v>-0.2873</v>
       </c>
       <c r="J390" t="n">
-        <v>-6.0291</v>
+        <v>-6.0333</v>
       </c>
     </row>
     <row r="391">
@@ -19829,10 +19829,10 @@
         <v>0.58</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.4508</v>
+        <v>-0.451</v>
       </c>
       <c r="J391" t="n">
-        <v>-9.466799999999999</v>
+        <v>-9.471</v>
       </c>
     </row>
     <row r="392">
@@ -20666,13 +20666,13 @@
         <v>15</v>
       </c>
       <c r="H412" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="I412" t="n">
-        <v>-0.1282</v>
+        <v>-0.1169</v>
       </c>
       <c r="J412" t="n">
-        <v>-1.923</v>
+        <v>-1.7535</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I413" t="n">
-        <v>-0.175</v>
+        <v>-0.1758</v>
       </c>
       <c r="J413" t="n">
-        <v>-2.625</v>
+        <v>-2.637</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>0.5</v>
       </c>
       <c r="I414" t="n">
-        <v>-0.4736</v>
+        <v>-0.4739</v>
       </c>
       <c r="J414" t="n">
-        <v>-7.104</v>
+        <v>-7.1085</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>0.36</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.5975</v>
+        <v>-0.5979</v>
       </c>
       <c r="J415" t="n">
-        <v>-8.9625</v>
+        <v>-8.968500000000001</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>0.27</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.678</v>
+        <v>-0.6783</v>
       </c>
       <c r="J416" t="n">
-        <v>-10.17</v>
+        <v>-10.1745</v>
       </c>
     </row>
     <row r="417">
@@ -22069,10 +22069,10 @@
         <v>1.4</v>
       </c>
       <c r="I447" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.9587</v>
       </c>
       <c r="J447" t="n">
-        <v>27.7878</v>
+        <v>27.8023</v>
       </c>
     </row>
     <row r="448">
@@ -22109,10 +22109,10 @@
         <v>1.22</v>
       </c>
       <c r="I448" t="n">
-        <v>0.593</v>
+        <v>0.5933</v>
       </c>
       <c r="J448" t="n">
-        <v>17.197</v>
+        <v>17.2057</v>
       </c>
     </row>
     <row r="449">
@@ -22146,13 +22146,13 @@
         <v>29</v>
       </c>
       <c r="H449" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="I449" t="n">
-        <v>0.3669</v>
+        <v>0.3422</v>
       </c>
       <c r="J449" t="n">
-        <v>10.6401</v>
+        <v>9.9238</v>
       </c>
     </row>
     <row r="450">
@@ -22189,10 +22189,10 @@
         <v>1.09</v>
       </c>
       <c r="I450" t="n">
-        <v>0.29</v>
+        <v>0.2903</v>
       </c>
       <c r="J450" t="n">
-        <v>8.41</v>
+        <v>8.418699999999999</v>
       </c>
     </row>
     <row r="451">
@@ -22229,10 +22229,10 @@
         <v>0.98</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.1281</v>
+        <v>-0.1277</v>
       </c>
       <c r="J451" t="n">
-        <v>-3.7149</v>
+        <v>-3.7033</v>
       </c>
     </row>
     <row r="452">
@@ -22666,13 +22666,13 @@
         <v>21</v>
       </c>
       <c r="H462" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="I462" t="n">
-        <v>0.3749</v>
+        <v>0.3925</v>
       </c>
       <c r="J462" t="n">
-        <v>7.8729</v>
+        <v>8.2425</v>
       </c>
     </row>
     <row r="463">
@@ -22709,10 +22709,10 @@
         <v>1</v>
       </c>
       <c r="I463" t="n">
-        <v>0.031</v>
+        <v>0.0299</v>
       </c>
       <c r="J463" t="n">
-        <v>0.651</v>
+        <v>0.6279</v>
       </c>
     </row>
     <row r="464">
@@ -22746,13 +22746,13 @@
         <v>21</v>
       </c>
       <c r="H464" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I464" t="n">
-        <v>-0.2368</v>
+        <v>-0.2274</v>
       </c>
       <c r="J464" t="n">
-        <v>-4.9728</v>
+        <v>-4.7754</v>
       </c>
     </row>
     <row r="465">
@@ -22789,10 +22789,10 @@
         <v>0.71</v>
       </c>
       <c r="I465" t="n">
-        <v>-0.322</v>
+        <v>-0.3225</v>
       </c>
       <c r="J465" t="n">
-        <v>-6.762</v>
+        <v>-6.7725</v>
       </c>
     </row>
     <row r="466">
@@ -22829,10 +22829,10 @@
         <v>0.52</v>
       </c>
       <c r="I466" t="n">
-        <v>-0.4917</v>
+        <v>-0.4921</v>
       </c>
       <c r="J466" t="n">
-        <v>-10.3257</v>
+        <v>-10.3341</v>
       </c>
     </row>
     <row r="467">
@@ -25466,13 +25466,13 @@
         <v>15</v>
       </c>
       <c r="H532" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="I532" t="n">
-        <v>1.4473</v>
+        <v>1.4357</v>
       </c>
       <c r="J532" t="n">
-        <v>21.7095</v>
+        <v>21.5355</v>
       </c>
     </row>
     <row r="533">
@@ -25509,10 +25509,10 @@
         <v>1.75</v>
       </c>
       <c r="I533" t="n">
-        <v>1.3641</v>
+        <v>1.3644</v>
       </c>
       <c r="J533" t="n">
-        <v>20.4615</v>
+        <v>20.466</v>
       </c>
     </row>
     <row r="534">
@@ -25549,10 +25549,10 @@
         <v>1.59</v>
       </c>
       <c r="I534" t="n">
-        <v>1.1703</v>
+        <v>1.1705</v>
       </c>
       <c r="J534" t="n">
-        <v>17.5545</v>
+        <v>17.5575</v>
       </c>
     </row>
     <row r="535">
@@ -25589,10 +25589,10 @@
         <v>1.47</v>
       </c>
       <c r="I535" t="n">
-        <v>1.016</v>
+        <v>1.0162</v>
       </c>
       <c r="J535" t="n">
-        <v>15.24</v>
+        <v>15.243</v>
       </c>
     </row>
     <row r="536">
@@ -25629,10 +25629,10 @@
         <v>1.18</v>
       </c>
       <c r="I536" t="n">
-        <v>0.4495</v>
+        <v>0.4498</v>
       </c>
       <c r="J536" t="n">
-        <v>6.7425</v>
+        <v>6.747</v>
       </c>
     </row>
     <row r="537">
@@ -26666,13 +26666,13 @@
         <v>19</v>
       </c>
       <c r="H562" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="I562" t="n">
-        <v>1.2863</v>
+        <v>1.2737</v>
       </c>
       <c r="J562" t="n">
-        <v>24.4397</v>
+        <v>24.2003</v>
       </c>
     </row>
     <row r="563">
@@ -26709,10 +26709,10 @@
         <v>1.54</v>
       </c>
       <c r="I563" t="n">
-        <v>1.142</v>
+        <v>1.1424</v>
       </c>
       <c r="J563" t="n">
-        <v>21.698</v>
+        <v>21.7056</v>
       </c>
     </row>
     <row r="564">
@@ -26749,10 +26749,10 @@
         <v>1.2</v>
       </c>
       <c r="I564" t="n">
-        <v>0.5352</v>
+        <v>0.5354</v>
       </c>
       <c r="J564" t="n">
-        <v>10.1688</v>
+        <v>10.1726</v>
       </c>
     </row>
     <row r="565">
@@ -26789,10 +26789,10 @@
         <v>1.19</v>
       </c>
       <c r="I565" t="n">
-        <v>0.513</v>
+        <v>0.5133</v>
       </c>
       <c r="J565" t="n">
-        <v>9.747</v>
+        <v>9.752700000000001</v>
       </c>
     </row>
     <row r="566">
@@ -26829,10 +26829,10 @@
         <v>0.83</v>
       </c>
       <c r="I566" t="n">
-        <v>-0.5687</v>
+        <v>-0.5684</v>
       </c>
       <c r="J566" t="n">
-        <v>-10.8053</v>
+        <v>-10.7996</v>
       </c>
     </row>
     <row r="567">
@@ -26869,10 +26869,10 @@
         <v>1.38</v>
       </c>
       <c r="I567" t="n">
-        <v>0.7669</v>
+        <v>0.766</v>
       </c>
       <c r="J567" t="n">
-        <v>14.5711</v>
+        <v>14.554</v>
       </c>
     </row>
     <row r="568">
@@ -26909,10 +26909,10 @@
         <v>0.9</v>
       </c>
       <c r="I568" t="n">
-        <v>-0.1382</v>
+        <v>-0.1383</v>
       </c>
       <c r="J568" t="n">
-        <v>-2.6258</v>
+        <v>-2.6277</v>
       </c>
     </row>
     <row r="569">
@@ -26946,13 +26946,13 @@
         <v>19</v>
       </c>
       <c r="H569" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="I569" t="n">
-        <v>-0.1908</v>
+        <v>-0.1807</v>
       </c>
       <c r="J569" t="n">
-        <v>-3.6252</v>
+        <v>-3.4333</v>
       </c>
     </row>
     <row r="570">
@@ -26989,10 +26989,10 @@
         <v>0.65</v>
       </c>
       <c r="I570" t="n">
-        <v>-0.3818</v>
+        <v>-0.382</v>
       </c>
       <c r="J570" t="n">
-        <v>-7.2542</v>
+        <v>-7.258</v>
       </c>
     </row>
     <row r="571">
@@ -27029,10 +27029,10 @@
         <v>0.62</v>
       </c>
       <c r="I571" t="n">
-        <v>-0.4087</v>
+        <v>-0.4089</v>
       </c>
       <c r="J571" t="n">
-        <v>-7.7653</v>
+        <v>-7.7691</v>
       </c>
     </row>
     <row r="572">
@@ -27269,10 +27269,10 @@
         <v>1.68</v>
       </c>
       <c r="I577" t="n">
-        <v>1.3358</v>
+        <v>1.3363</v>
       </c>
       <c r="J577" t="n">
-        <v>30.7234</v>
+        <v>30.7349</v>
       </c>
     </row>
     <row r="578">
@@ -27309,10 +27309,10 @@
         <v>1.5</v>
       </c>
       <c r="I578" t="n">
-        <v>1.0968</v>
+        <v>1.0972</v>
       </c>
       <c r="J578" t="n">
-        <v>25.2264</v>
+        <v>25.2356</v>
       </c>
     </row>
     <row r="579">
@@ -27349,10 +27349,10 @@
         <v>1.28</v>
       </c>
       <c r="I579" t="n">
-        <v>0.7065</v>
+        <v>0.7068</v>
       </c>
       <c r="J579" t="n">
-        <v>16.2495</v>
+        <v>16.2564</v>
       </c>
     </row>
     <row r="580">
@@ -27386,13 +27386,13 @@
         <v>23</v>
       </c>
       <c r="H580" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="I580" t="n">
-        <v>0.1316</v>
+        <v>0.0983</v>
       </c>
       <c r="J580" t="n">
-        <v>3.0268</v>
+        <v>2.2609</v>
       </c>
     </row>
     <row r="581">
@@ -27429,10 +27429,10 @@
         <v>0.68</v>
       </c>
       <c r="I581" t="n">
-        <v>-0.8923</v>
+        <v>-0.892</v>
       </c>
       <c r="J581" t="n">
-        <v>-20.5229</v>
+        <v>-20.516</v>
       </c>
     </row>
     <row r="582">
@@ -28266,13 +28266,13 @@
         <v>22</v>
       </c>
       <c r="H602" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="I602" t="n">
-        <v>1.3406</v>
+        <v>1.3533</v>
       </c>
       <c r="J602" t="n">
-        <v>29.4932</v>
+        <v>29.7726</v>
       </c>
     </row>
     <row r="603">
@@ -28309,10 +28309,10 @@
         <v>1.19</v>
       </c>
       <c r="I603" t="n">
-        <v>0.5334</v>
+        <v>0.533</v>
       </c>
       <c r="J603" t="n">
-        <v>11.7348</v>
+        <v>11.726</v>
       </c>
     </row>
     <row r="604">
@@ -28349,10 +28349,10 @@
         <v>1.17</v>
       </c>
       <c r="I604" t="n">
-        <v>0.4881</v>
+        <v>0.4878</v>
       </c>
       <c r="J604" t="n">
-        <v>10.7382</v>
+        <v>10.7316</v>
       </c>
     </row>
     <row r="605">
@@ -28389,10 +28389,10 @@
         <v>0.88</v>
       </c>
       <c r="I605" t="n">
-        <v>-0.4189</v>
+        <v>-0.4193</v>
       </c>
       <c r="J605" t="n">
-        <v>-9.2158</v>
+        <v>-9.224600000000001</v>
       </c>
     </row>
     <row r="606">
@@ -28429,10 +28429,10 @@
         <v>0.73</v>
       </c>
       <c r="I606" t="n">
-        <v>-0.7685</v>
+        <v>-0.7688</v>
       </c>
       <c r="J606" t="n">
-        <v>-16.907</v>
+        <v>-16.9136</v>
       </c>
     </row>
     <row r="607">
@@ -28469,10 +28469,10 @@
         <v>1.17</v>
       </c>
       <c r="I607" t="n">
-        <v>0.4076</v>
+        <v>0.4082</v>
       </c>
       <c r="J607" t="n">
-        <v>8.9672</v>
+        <v>8.980399999999999</v>
       </c>
     </row>
     <row r="608">
@@ -28506,13 +28506,13 @@
         <v>22</v>
       </c>
       <c r="H608" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="I608" t="n">
-        <v>0.0145</v>
+        <v>-0.0172</v>
       </c>
       <c r="J608" t="n">
-        <v>0.319</v>
+        <v>-0.3784</v>
       </c>
     </row>
     <row r="609">
@@ -28549,10 +28549,10 @@
         <v>0.96</v>
       </c>
       <c r="I609" t="n">
-        <v>-0.0658</v>
+        <v>-0.0655</v>
       </c>
       <c r="J609" t="n">
-        <v>-1.4476</v>
+        <v>-1.441</v>
       </c>
     </row>
     <row r="610">
@@ -28589,10 +28589,10 @@
         <v>0.86</v>
       </c>
       <c r="I610" t="n">
-        <v>-0.1822</v>
+        <v>-0.1821</v>
       </c>
       <c r="J610" t="n">
-        <v>-4.0084</v>
+        <v>-4.0062</v>
       </c>
     </row>
     <row r="611">
@@ -28629,10 +28629,10 @@
         <v>0.52</v>
       </c>
       <c r="I611" t="n">
-        <v>-0.4981</v>
+        <v>-0.4979</v>
       </c>
       <c r="J611" t="n">
-        <v>-10.9582</v>
+        <v>-10.9538</v>
       </c>
     </row>
     <row r="612">
@@ -29066,7 +29066,7 @@
         <v>24</v>
       </c>
       <c r="H622" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="I622" t="n">
         <v>1.9372</v>
@@ -29109,10 +29109,10 @@
         <v>1.2</v>
       </c>
       <c r="I623" t="n">
-        <v>0.5462</v>
+        <v>0.5464</v>
       </c>
       <c r="J623" t="n">
-        <v>13.1088</v>
+        <v>13.1136</v>
       </c>
     </row>
     <row r="624">
@@ -29149,10 +29149,10 @@
         <v>0.97</v>
       </c>
       <c r="I624" t="n">
-        <v>-0.1694</v>
+        <v>-0.169</v>
       </c>
       <c r="J624" t="n">
-        <v>-4.0656</v>
+        <v>-4.056</v>
       </c>
     </row>
     <row r="625">
@@ -29189,10 +29189,10 @@
         <v>0.67</v>
       </c>
       <c r="I625" t="n">
-        <v>-0.9059</v>
+        <v>-0.9056</v>
       </c>
       <c r="J625" t="n">
-        <v>-21.7416</v>
+        <v>-21.7344</v>
       </c>
     </row>
     <row r="626">
@@ -29229,10 +29229,10 @@
         <v>0.58</v>
       </c>
       <c r="I626" t="n">
-        <v>-1.0881</v>
+        <v>-1.0879</v>
       </c>
       <c r="J626" t="n">
-        <v>-26.1144</v>
+        <v>-26.1096</v>
       </c>
     </row>
     <row r="627">
@@ -29266,13 +29266,13 @@
         <v>24</v>
       </c>
       <c r="H627" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="I627" t="n">
-        <v>0.9855</v>
+        <v>0.9972</v>
       </c>
       <c r="J627" t="n">
-        <v>23.652</v>
+        <v>23.9328</v>
       </c>
     </row>
     <row r="628">
@@ -29309,10 +29309,10 @@
         <v>1.13</v>
       </c>
       <c r="I628" t="n">
-        <v>0.3055</v>
+        <v>0.3051</v>
       </c>
       <c r="J628" t="n">
-        <v>7.332</v>
+        <v>7.3224</v>
       </c>
     </row>
     <row r="629">
@@ -29349,10 +29349,10 @@
         <v>0.89</v>
       </c>
       <c r="I629" t="n">
-        <v>-0.1601</v>
+        <v>-0.1603</v>
       </c>
       <c r="J629" t="n">
-        <v>-3.8424</v>
+        <v>-3.8472</v>
       </c>
     </row>
     <row r="630">
@@ -29389,10 +29389,10 @@
         <v>0.85</v>
       </c>
       <c r="I630" t="n">
-        <v>-0.2034</v>
+        <v>-0.2036</v>
       </c>
       <c r="J630" t="n">
-        <v>-4.8816</v>
+        <v>-4.8864</v>
       </c>
     </row>
     <row r="631">
@@ -29429,10 +29429,10 @@
         <v>0.67</v>
       </c>
       <c r="I631" t="n">
-        <v>-0.3769</v>
+        <v>-0.3771</v>
       </c>
       <c r="J631" t="n">
-        <v>-9.0456</v>
+        <v>-9.0504</v>
       </c>
     </row>
     <row r="632">
@@ -30069,10 +30069,10 @@
         <v>1.29</v>
       </c>
       <c r="I647" t="n">
-        <v>0.473</v>
+        <v>0.4725</v>
       </c>
       <c r="J647" t="n">
-        <v>13.244</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="648">
@@ -30109,10 +30109,10 @@
         <v>1.05</v>
       </c>
       <c r="I648" t="n">
-        <v>0.1259</v>
+        <v>0.1256</v>
       </c>
       <c r="J648" t="n">
-        <v>3.5252</v>
+        <v>3.5168</v>
       </c>
     </row>
     <row r="649">
@@ -30149,10 +30149,10 @@
         <v>0.85</v>
       </c>
       <c r="I649" t="n">
-        <v>-0.1949</v>
+        <v>-0.1951</v>
       </c>
       <c r="J649" t="n">
-        <v>-5.4572</v>
+        <v>-5.4628</v>
       </c>
     </row>
     <row r="650">
@@ -30186,13 +30186,13 @@
         <v>28</v>
       </c>
       <c r="H650" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="I650" t="n">
-        <v>-0.2156</v>
+        <v>-0.2055</v>
       </c>
       <c r="J650" t="n">
-        <v>-6.0368</v>
+        <v>-5.754</v>
       </c>
     </row>
     <row r="651">
@@ -30229,10 +30229,10 @@
         <v>0.62</v>
       </c>
       <c r="I651" t="n">
-        <v>-0.4133</v>
+        <v>-0.4135</v>
       </c>
       <c r="J651" t="n">
-        <v>-11.5724</v>
+        <v>-11.578</v>
       </c>
     </row>
     <row r="652">
@@ -31666,13 +31666,13 @@
         <v>17</v>
       </c>
       <c r="H687" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I687" t="n">
-        <v>-0.0034</v>
+        <v>0.0387</v>
       </c>
       <c r="J687" t="n">
-        <v>-0.0578</v>
+        <v>0.6579</v>
       </c>
     </row>
     <row r="688">
@@ -31709,10 +31709,10 @@
         <v>0.92</v>
       </c>
       <c r="I688" t="n">
-        <v>-0.1061</v>
+        <v>-0.1064</v>
       </c>
       <c r="J688" t="n">
-        <v>-1.8037</v>
+        <v>-1.8088</v>
       </c>
     </row>
     <row r="689">
@@ -31749,10 +31749,10 @@
         <v>0.77</v>
       </c>
       <c r="I689" t="n">
-        <v>-0.2629</v>
+        <v>-0.2631</v>
       </c>
       <c r="J689" t="n">
-        <v>-4.4693</v>
+        <v>-4.4727</v>
       </c>
     </row>
     <row r="690">
@@ -31789,10 +31789,10 @@
         <v>0.75</v>
       </c>
       <c r="I690" t="n">
-        <v>-0.2818</v>
+        <v>-0.282</v>
       </c>
       <c r="J690" t="n">
-        <v>-4.7906</v>
+        <v>-4.794</v>
       </c>
     </row>
     <row r="691">
@@ -31829,10 +31829,10 @@
         <v>0.6</v>
       </c>
       <c r="I691" t="n">
-        <v>-0.4186</v>
+        <v>-0.4188</v>
       </c>
       <c r="J691" t="n">
-        <v>-7.1162</v>
+        <v>-7.1196</v>
       </c>
     </row>
     <row r="692">
@@ -32466,13 +32466,13 @@
         <v>23</v>
       </c>
       <c r="H707" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="I707" t="n">
-        <v>0.5562</v>
+        <v>0.5718</v>
       </c>
       <c r="J707" t="n">
-        <v>12.7926</v>
+        <v>13.1514</v>
       </c>
     </row>
     <row r="708">
@@ -32509,10 +32509,10 @@
         <v>1.03</v>
       </c>
       <c r="I708" t="n">
-        <v>0.1033</v>
+        <v>0.103</v>
       </c>
       <c r="J708" t="n">
-        <v>2.3759</v>
+        <v>2.369</v>
       </c>
     </row>
     <row r="709">
@@ -32549,10 +32549,10 @@
         <v>0.89</v>
       </c>
       <c r="I709" t="n">
-        <v>-0.1561</v>
+        <v>-0.1563</v>
       </c>
       <c r="J709" t="n">
-        <v>-3.5903</v>
+        <v>-3.5949</v>
       </c>
     </row>
     <row r="710">
@@ -32589,10 +32589,10 @@
         <v>0.85</v>
       </c>
       <c r="I710" t="n">
-        <v>-0.1993</v>
+        <v>-0.1995</v>
       </c>
       <c r="J710" t="n">
-        <v>-4.5839</v>
+        <v>-4.5885</v>
       </c>
     </row>
     <row r="711">
@@ -32629,16 +32629,16 @@
         <v>0.84</v>
       </c>
       <c r="I711" t="n">
-        <v>-0.2097</v>
+        <v>-0.2099</v>
       </c>
       <c r="J711" t="n">
-        <v>-4.8231</v>
+        <v>-4.8277</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>Lucaozy</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -32666,19 +32666,19 @@
         <v>16</v>
       </c>
       <c r="H712" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="I712" t="n">
-        <v>1.4559</v>
+        <v>1.4672</v>
       </c>
       <c r="J712" t="n">
-        <v>23.2944</v>
+        <v>23.4752</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>Lucaozy</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -32706,13 +32706,13 @@
         <v>16</v>
       </c>
       <c r="H713" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="I713" t="n">
-        <v>1.444</v>
+        <v>1.4553</v>
       </c>
       <c r="J713" t="n">
-        <v>23.104</v>
+        <v>23.2848</v>
       </c>
     </row>
     <row r="714">
@@ -32749,10 +32749,10 @@
         <v>1.39</v>
       </c>
       <c r="I714" t="n">
-        <v>0.887</v>
+        <v>0.8865</v>
       </c>
       <c r="J714" t="n">
-        <v>14.192</v>
+        <v>14.184</v>
       </c>
     </row>
     <row r="715">
@@ -32789,10 +32789,10 @@
         <v>1.36</v>
       </c>
       <c r="I715" t="n">
-        <v>0.8304</v>
+        <v>0.8299</v>
       </c>
       <c r="J715" t="n">
-        <v>13.2864</v>
+        <v>13.2784</v>
       </c>
     </row>
     <row r="716">
@@ -32829,10 +32829,10 @@
         <v>1.14</v>
       </c>
       <c r="I716" t="n">
-        <v>0.3637</v>
+        <v>0.3632</v>
       </c>
       <c r="J716" t="n">
-        <v>5.8192</v>
+        <v>5.8112</v>
       </c>
     </row>
     <row r="717">
@@ -32869,10 +32869,10 @@
         <v>0.79</v>
       </c>
       <c r="I717" t="n">
-        <v>-0.2036</v>
+        <v>-0.2029</v>
       </c>
       <c r="J717" t="n">
-        <v>-3.2576</v>
+        <v>-3.2464</v>
       </c>
     </row>
     <row r="718">
@@ -32909,10 +32909,10 @@
         <v>0.7</v>
       </c>
       <c r="I718" t="n">
-        <v>-0.2976</v>
+        <v>-0.2971</v>
       </c>
       <c r="J718" t="n">
-        <v>-4.7616</v>
+        <v>-4.7536</v>
       </c>
     </row>
     <row r="719">
@@ -32946,13 +32946,13 @@
         <v>16</v>
       </c>
       <c r="H719" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="I719" t="n">
-        <v>-0.4246</v>
+        <v>-0.4328</v>
       </c>
       <c r="J719" t="n">
-        <v>-6.7936</v>
+        <v>-6.9248</v>
       </c>
     </row>
     <row r="720">
@@ -32989,10 +32989,10 @@
         <v>0.48</v>
       </c>
       <c r="I720" t="n">
-        <v>-0.494</v>
+        <v>-0.4937</v>
       </c>
       <c r="J720" t="n">
-        <v>-7.904</v>
+        <v>-7.8992</v>
       </c>
     </row>
     <row r="721">
@@ -33029,10 +33029,10 @@
         <v>0.35</v>
       </c>
       <c r="I721" t="n">
-        <v>-0.6091</v>
+        <v>-0.6088</v>
       </c>
       <c r="J721" t="n">
-        <v>-9.7456</v>
+        <v>-9.7408</v>
       </c>
     </row>
     <row r="722">
@@ -33469,10 +33469,10 @@
         <v>1.42</v>
       </c>
       <c r="I732" t="n">
-        <v>0.8015</v>
+        <v>0.8023</v>
       </c>
       <c r="J732" t="n">
-        <v>16.8315</v>
+        <v>16.8483</v>
       </c>
     </row>
     <row r="733">
@@ -33509,10 +33509,10 @@
         <v>1.21</v>
       </c>
       <c r="I733" t="n">
-        <v>0.4655</v>
+        <v>0.4661</v>
       </c>
       <c r="J733" t="n">
-        <v>9.775499999999999</v>
+        <v>9.7881</v>
       </c>
     </row>
     <row r="734">
@@ -33546,13 +33546,13 @@
         <v>21</v>
       </c>
       <c r="H734" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="I734" t="n">
-        <v>-0.1964</v>
+        <v>-0.2066</v>
       </c>
       <c r="J734" t="n">
-        <v>-4.1244</v>
+        <v>-4.3386</v>
       </c>
     </row>
     <row r="735">
@@ -33589,10 +33589,10 @@
         <v>0.78</v>
       </c>
       <c r="I735" t="n">
-        <v>-0.2668</v>
+        <v>-0.2666</v>
       </c>
       <c r="J735" t="n">
-        <v>-5.6028</v>
+        <v>-5.5986</v>
       </c>
     </row>
     <row r="736">
@@ -33629,10 +33629,10 @@
         <v>0.46</v>
       </c>
       <c r="I736" t="n">
-        <v>-0.5524</v>
+        <v>-0.5523</v>
       </c>
       <c r="J736" t="n">
-        <v>-11.6004</v>
+        <v>-11.5983</v>
       </c>
     </row>
     <row r="737">
@@ -36269,10 +36269,10 @@
         <v>1.6</v>
       </c>
       <c r="I802" t="n">
-        <v>1.2401</v>
+        <v>1.2406</v>
       </c>
       <c r="J802" t="n">
-        <v>27.2822</v>
+        <v>27.2932</v>
       </c>
     </row>
     <row r="803">
@@ -36309,10 +36309,10 @@
         <v>1.38</v>
       </c>
       <c r="I803" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9123</v>
       </c>
       <c r="J803" t="n">
-        <v>20.0596</v>
+        <v>20.0706</v>
       </c>
     </row>
     <row r="804">
@@ -36346,13 +36346,13 @@
         <v>22</v>
       </c>
       <c r="H804" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="I804" t="n">
-        <v>0.2841</v>
+        <v>0.2573</v>
       </c>
       <c r="J804" t="n">
-        <v>6.2502</v>
+        <v>5.6606</v>
       </c>
     </row>
     <row r="805">
@@ -36389,10 +36389,10 @@
         <v>0.99</v>
       </c>
       <c r="I805" t="n">
-        <v>-0.093</v>
+        <v>-0.0927</v>
       </c>
       <c r="J805" t="n">
-        <v>-2.046</v>
+        <v>-2.0394</v>
       </c>
     </row>
     <row r="806">
@@ -36429,10 +36429,10 @@
         <v>0.93</v>
       </c>
       <c r="I806" t="n">
-        <v>-0.2968</v>
+        <v>-0.2964</v>
       </c>
       <c r="J806" t="n">
-        <v>-6.5296</v>
+        <v>-6.5208</v>
       </c>
     </row>
     <row r="807">
@@ -36466,13 +36466,13 @@
         <v>22</v>
       </c>
       <c r="H807" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="I807" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7368</v>
       </c>
       <c r="J807" t="n">
-        <v>15.8906</v>
+        <v>16.2096</v>
       </c>
     </row>
     <row r="808">
@@ -36509,10 +36509,10 @@
         <v>1.01</v>
       </c>
       <c r="I808" t="n">
-        <v>0.0437</v>
+        <v>0.0435</v>
       </c>
       <c r="J808" t="n">
-        <v>0.9614</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="809">
@@ -36549,10 +36549,10 @@
         <v>1.01</v>
       </c>
       <c r="I809" t="n">
-        <v>0.0437</v>
+        <v>0.0435</v>
       </c>
       <c r="J809" t="n">
-        <v>0.9614</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="810">
@@ -36589,10 +36589,10 @@
         <v>0.97</v>
       </c>
       <c r="I810" t="n">
-        <v>-0.0579</v>
+        <v>-0.0581</v>
       </c>
       <c r="J810" t="n">
-        <v>-1.2738</v>
+        <v>-1.2782</v>
       </c>
     </row>
     <row r="811">
@@ -36629,10 +36629,10 @@
         <v>0.61</v>
       </c>
       <c r="I811" t="n">
-        <v>-0.4281</v>
+        <v>-0.4283</v>
       </c>
       <c r="J811" t="n">
-        <v>-9.418200000000001</v>
+        <v>-9.422599999999999</v>
       </c>
     </row>
     <row r="812">
@@ -36866,13 +36866,13 @@
         <v>21</v>
       </c>
       <c r="H817" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I817" t="n">
-        <v>0.1881</v>
+        <v>0.2108</v>
       </c>
       <c r="J817" t="n">
-        <v>3.9501</v>
+        <v>4.4268</v>
       </c>
     </row>
     <row r="818">
@@ -36909,10 +36909,10 @@
         <v>0.83</v>
       </c>
       <c r="I818" t="n">
-        <v>-0.2072</v>
+        <v>-0.2073</v>
       </c>
       <c r="J818" t="n">
-        <v>-4.3512</v>
+        <v>-4.3533</v>
       </c>
     </row>
     <row r="819">
@@ -36949,10 +36949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I819" t="n">
-        <v>-0.2264</v>
+        <v>-0.2266</v>
       </c>
       <c r="J819" t="n">
-        <v>-4.7544</v>
+        <v>-4.7586</v>
       </c>
     </row>
     <row r="820">
@@ -36989,10 +36989,10 @@
         <v>0.79</v>
       </c>
       <c r="I820" t="n">
-        <v>-0.2457</v>
+        <v>-0.2459</v>
       </c>
       <c r="J820" t="n">
-        <v>-5.1597</v>
+        <v>-5.1639</v>
       </c>
     </row>
     <row r="821">
@@ -37029,10 +37029,10 @@
         <v>0.65</v>
       </c>
       <c r="I821" t="n">
-        <v>-0.376</v>
+        <v>-0.3763</v>
       </c>
       <c r="J821" t="n">
-        <v>-7.896</v>
+        <v>-7.9023</v>
       </c>
     </row>
     <row r="822">
@@ -37069,10 +37069,10 @@
         <v>1.94</v>
       </c>
       <c r="I822" t="n">
-        <v>1.6277</v>
+        <v>1.6317</v>
       </c>
       <c r="J822" t="n">
-        <v>29.2986</v>
+        <v>29.3706</v>
       </c>
     </row>
     <row r="823">
@@ -37106,13 +37106,13 @@
         <v>18</v>
       </c>
       <c r="H823" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="I823" t="n">
-        <v>1.1023</v>
+        <v>1.078</v>
       </c>
       <c r="J823" t="n">
-        <v>19.8414</v>
+        <v>19.404</v>
       </c>
     </row>
     <row r="824">
@@ -37146,13 +37146,13 @@
         <v>18</v>
       </c>
       <c r="H824" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="I824" t="n">
-        <v>1.1023</v>
+        <v>1.0505</v>
       </c>
       <c r="J824" t="n">
-        <v>19.8414</v>
+        <v>18.909</v>
       </c>
     </row>
     <row r="825">
@@ -37186,13 +37186,13 @@
         <v>18</v>
       </c>
       <c r="H825" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="I825" t="n">
-        <v>0.4084</v>
+        <v>0.3869</v>
       </c>
       <c r="J825" t="n">
-        <v>7.3512</v>
+        <v>6.9642</v>
       </c>
     </row>
     <row r="826">
@@ -37226,13 +37226,13 @@
         <v>18</v>
       </c>
       <c r="H826" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="I826" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.9073</v>
       </c>
       <c r="J826" t="n">
-        <v>-15.9948</v>
+        <v>-16.3314</v>
       </c>
     </row>
     <row r="827">
@@ -37269,10 +37269,10 @@
         <v>1.04</v>
       </c>
       <c r="I827" t="n">
-        <v>0.1592</v>
+        <v>0.1575</v>
       </c>
       <c r="J827" t="n">
-        <v>2.8656</v>
+        <v>2.835</v>
       </c>
     </row>
     <row r="828">
@@ -37306,13 +37306,13 @@
         <v>18</v>
       </c>
       <c r="H828" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I828" t="n">
-        <v>-0.0091</v>
+        <v>0.0277</v>
       </c>
       <c r="J828" t="n">
-        <v>-0.1638</v>
+        <v>0.4986</v>
       </c>
     </row>
     <row r="829">
@@ -37349,10 +37349,10 @@
         <v>0.97</v>
       </c>
       <c r="I829" t="n">
-        <v>-0.0434</v>
+        <v>-0.0442</v>
       </c>
       <c r="J829" t="n">
-        <v>-0.7812</v>
+        <v>-0.7956</v>
       </c>
     </row>
     <row r="830">
@@ -37386,13 +37386,13 @@
         <v>18</v>
       </c>
       <c r="H830" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="I830" t="n">
-        <v>-0.2852</v>
+        <v>-0.2668</v>
       </c>
       <c r="J830" t="n">
-        <v>-5.1336</v>
+        <v>-4.8024</v>
       </c>
     </row>
     <row r="831">
@@ -37429,10 +37429,10 @@
         <v>0.45</v>
       </c>
       <c r="I831" t="n">
-        <v>-0.5523</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="J831" t="n">
-        <v>-9.9414</v>
+        <v>-9.952199999999999</v>
       </c>
     </row>
     <row r="832">
@@ -39069,10 +39069,10 @@
         <v>1.23</v>
       </c>
       <c r="I872" t="n">
-        <v>0.4904</v>
+        <v>0.4909</v>
       </c>
       <c r="J872" t="n">
-        <v>16.6736</v>
+        <v>16.6906</v>
       </c>
     </row>
     <row r="873">
@@ -39109,10 +39109,10 @@
         <v>1.17</v>
       </c>
       <c r="I873" t="n">
-        <v>0.3873</v>
+        <v>0.3878</v>
       </c>
       <c r="J873" t="n">
-        <v>13.1682</v>
+        <v>13.1852</v>
       </c>
     </row>
     <row r="874">
@@ -39149,16 +39149,16 @@
         <v>0.83</v>
       </c>
       <c r="I874" t="n">
-        <v>-0.22</v>
+        <v>-0.2198</v>
       </c>
       <c r="J874" t="n">
-        <v>-7.48</v>
+        <v>-7.4732</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>Lucaozy</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
@@ -39186,19 +39186,19 @@
         <v>34</v>
       </c>
       <c r="H875" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I875" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="J875" t="n">
-        <v>-7.48</v>
+        <v>-7.82</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>Lucaozy</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
@@ -39229,10 +39229,10 @@
         <v>0.82</v>
       </c>
       <c r="I876" t="n">
-        <v>-0.2302</v>
+        <v>-0.23</v>
       </c>
       <c r="J876" t="n">
-        <v>-7.8268</v>
+        <v>-7.82</v>
       </c>
     </row>
     <row r="877">
@@ -39466,13 +39466,13 @@
         <v>17</v>
       </c>
       <c r="H882" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="I882" t="n">
-        <v>0.623</v>
+        <v>0.6499</v>
       </c>
       <c r="J882" t="n">
-        <v>10.591</v>
+        <v>11.0483</v>
       </c>
     </row>
     <row r="883">
@@ -39509,10 +39509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I883" t="n">
-        <v>-0.3272</v>
+        <v>-0.3286</v>
       </c>
       <c r="J883" t="n">
-        <v>-5.5624</v>
+        <v>-5.5862</v>
       </c>
     </row>
     <row r="884">
@@ -39546,13 +39546,13 @@
         <v>17</v>
       </c>
       <c r="H884" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I884" t="n">
-        <v>-0.3539</v>
+        <v>-0.3286</v>
       </c>
       <c r="J884" t="n">
-        <v>-6.0163</v>
+        <v>-5.5862</v>
       </c>
     </row>
     <row r="885">
@@ -39586,13 +39586,13 @@
         <v>17</v>
       </c>
       <c r="H885" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="I885" t="n">
-        <v>-0.4073</v>
+        <v>-0.4002</v>
       </c>
       <c r="J885" t="n">
-        <v>-6.9241</v>
+        <v>-6.8034</v>
       </c>
     </row>
     <row r="886">
@@ -39626,13 +39626,13 @@
         <v>17</v>
       </c>
       <c r="H886" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="I886" t="n">
-        <v>-0.6082</v>
+        <v>-0.6011</v>
       </c>
       <c r="J886" t="n">
-        <v>-10.3394</v>
+        <v>-10.2187</v>
       </c>
     </row>
     <row r="887">
@@ -39669,10 +39669,10 @@
         <v>1.81</v>
       </c>
       <c r="I887" t="n">
-        <v>1.4523</v>
+        <v>1.4545</v>
       </c>
       <c r="J887" t="n">
-        <v>24.6891</v>
+        <v>24.7265</v>
       </c>
     </row>
     <row r="888">
@@ -39706,13 +39706,13 @@
         <v>17</v>
       </c>
       <c r="H888" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="I888" t="n">
-        <v>1.416</v>
+        <v>1.3937</v>
       </c>
       <c r="J888" t="n">
-        <v>24.072</v>
+        <v>23.6929</v>
       </c>
     </row>
     <row r="889">
@@ -39749,10 +39749,10 @@
         <v>1.34</v>
       </c>
       <c r="I889" t="n">
-        <v>0.7986</v>
+        <v>0.8001</v>
       </c>
       <c r="J889" t="n">
-        <v>13.5762</v>
+        <v>13.6017</v>
       </c>
     </row>
     <row r="890">
@@ -39786,13 +39786,13 @@
         <v>17</v>
       </c>
       <c r="H890" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="I890" t="n">
-        <v>0.7792</v>
+        <v>0.7415</v>
       </c>
       <c r="J890" t="n">
-        <v>13.2464</v>
+        <v>12.6055</v>
       </c>
     </row>
     <row r="891">
@@ -39826,13 +39826,13 @@
         <v>17</v>
       </c>
       <c r="H891" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="I891" t="n">
-        <v>-0.0141</v>
+        <v>-0.1319</v>
       </c>
       <c r="J891" t="n">
-        <v>-0.2397</v>
+        <v>-2.2423</v>
       </c>
     </row>
     <row r="892">
@@ -42266,13 +42266,13 @@
         <v>24</v>
       </c>
       <c r="H952" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="I952" t="n">
-        <v>0.4616</v>
+        <v>0.4499</v>
       </c>
       <c r="J952" t="n">
-        <v>11.0784</v>
+        <v>10.7976</v>
       </c>
     </row>
     <row r="953">
@@ -42309,10 +42309,10 @@
         <v>1.24</v>
       </c>
       <c r="I953" t="n">
-        <v>0.3759</v>
+        <v>0.3762</v>
       </c>
       <c r="J953" t="n">
-        <v>9.021599999999999</v>
+        <v>9.0288</v>
       </c>
     </row>
     <row r="954">
@@ -42349,10 +42349,10 @@
         <v>1.12</v>
       </c>
       <c r="I954" t="n">
-        <v>0.2165</v>
+        <v>0.2167</v>
       </c>
       <c r="J954" t="n">
-        <v>5.196</v>
+        <v>5.2008</v>
       </c>
     </row>
     <row r="955">
@@ -42389,10 +42389,10 @@
         <v>1</v>
       </c>
       <c r="I955" t="n">
-        <v>-0.0064</v>
+        <v>-0.0063</v>
       </c>
       <c r="J955" t="n">
-        <v>-0.1536</v>
+        <v>-0.1512</v>
       </c>
     </row>
     <row r="956">
@@ -42429,10 +42429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I956" t="n">
-        <v>-0.2508</v>
+        <v>-0.2506</v>
       </c>
       <c r="J956" t="n">
-        <v>-6.0192</v>
+        <v>-6.0144</v>
       </c>
     </row>
     <row r="957">
@@ -42469,10 +42469,10 @@
         <v>1.43</v>
       </c>
       <c r="I957" t="n">
-        <v>0.575</v>
+        <v>0.5742</v>
       </c>
       <c r="J957" t="n">
-        <v>13.8</v>
+        <v>13.7808</v>
       </c>
     </row>
     <row r="958">
@@ -42509,10 +42509,10 @@
         <v>1.36</v>
       </c>
       <c r="I958" t="n">
-        <v>0.4983</v>
+        <v>0.4975</v>
       </c>
       <c r="J958" t="n">
-        <v>11.9592</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="959">
@@ -42546,13 +42546,13 @@
         <v>24</v>
       </c>
       <c r="H959" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I959" t="n">
-        <v>-0.1175</v>
+        <v>-0.1052</v>
       </c>
       <c r="J959" t="n">
-        <v>-2.82</v>
+        <v>-2.5248</v>
       </c>
     </row>
     <row r="960">
@@ -42589,10 +42589,10 @@
         <v>0.92</v>
       </c>
       <c r="I960" t="n">
-        <v>-0.1297</v>
+        <v>-0.13</v>
       </c>
       <c r="J960" t="n">
-        <v>-3.1128</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="961">
@@ -42626,13 +42626,13 @@
         <v>24</v>
       </c>
       <c r="H961" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="I961" t="n">
-        <v>-0.3353</v>
+        <v>-0.3263</v>
       </c>
       <c r="J961" t="n">
-        <v>-8.0472</v>
+        <v>-7.8312</v>
       </c>
     </row>
     <row r="962">
@@ -43266,13 +43266,13 @@
         <v>24</v>
       </c>
       <c r="H977" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="I977" t="n">
-        <v>1.0015</v>
+        <v>0.99</v>
       </c>
       <c r="J977" t="n">
-        <v>24.036</v>
+        <v>23.76</v>
       </c>
     </row>
     <row r="978">
@@ -43309,10 +43309,10 @@
         <v>1.15</v>
       </c>
       <c r="I978" t="n">
-        <v>0.3371</v>
+        <v>0.3374</v>
       </c>
       <c r="J978" t="n">
-        <v>8.090400000000001</v>
+        <v>8.0976</v>
       </c>
     </row>
     <row r="979">
@@ -43349,10 +43349,10 @@
         <v>1.07</v>
       </c>
       <c r="I979" t="n">
-        <v>0.1851</v>
+        <v>0.1853</v>
       </c>
       <c r="J979" t="n">
-        <v>4.4424</v>
+        <v>4.4472</v>
       </c>
     </row>
     <row r="980">
@@ -43389,10 +43389,10 @@
         <v>0.91</v>
       </c>
       <c r="I980" t="n">
-        <v>-0.1395</v>
+        <v>-0.1393</v>
       </c>
       <c r="J980" t="n">
-        <v>-3.348</v>
+        <v>-3.3432</v>
       </c>
     </row>
     <row r="981">
@@ -43429,10 +43429,10 @@
         <v>0.52</v>
       </c>
       <c r="I981" t="n">
-        <v>-0.5094</v>
+        <v>-0.5093</v>
       </c>
       <c r="J981" t="n">
-        <v>-12.2256</v>
+        <v>-12.2232</v>
       </c>
     </row>
     <row r="982">
